--- a/Oefenbestand-verzuim-en-uren.xlsx
+++ b/Oefenbestand-verzuim-en-uren.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Nathalie1/Documents/Mijn Documenten Archief/02 Eigen bedrijf/Promoveren/Workshops per klant/Klaar voor morgen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C25172C2-AC8E-6B4B-9FA9-2EA20E69EC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B90B3EB-027E-3641-BDC9-56844268D108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2680" yWindow="1600" windowWidth="28240" windowHeight="17240" xr2:uid="{BC64122E-F4AE-EB4B-A0BC-FA6DC2C1C7E6}"/>
+    <workbookView xWindow="2680" yWindow="9400" windowWidth="28240" windowHeight="17240" xr2:uid="{BC64122E-F4AE-EB4B-A0BC-FA6DC2C1C7E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Toelichting" sheetId="2" r:id="rId1"/>
     <sheet name="Registratie" sheetId="1" r:id="rId2"/>
+    <sheet name="Antwoordmodel" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,8 +40,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="125">
   <si>
     <t>Maand</t>
   </si>
@@ -323,17 +346,111 @@
   <si>
     <t>Zet nooit echte verzuimgegevens met namen in een AI-tool. Verzuim is een bijzonder persoonsgegeven — anonimiseer eerst of gebruik alleen totalen.</t>
   </si>
+  <si>
+    <t>Antwoordmodel — alleen voor de trainer</t>
+  </si>
+  <si>
+    <t>Alle cijfers zijn formules op het tabblad Registratie. Fictieve data — elk patroon is verzonnen.</t>
+  </si>
+  <si>
+    <t>1. Verzuim per afdeling, heel 2025 (vraag 1)</t>
+  </si>
+  <si>
+    <t>waarvan langdurig</t>
+  </si>
+  <si>
+    <t>Medewerkers</t>
+  </si>
+  <si>
+    <t>Totaal</t>
+  </si>
+  <si>
+    <t>2. Verzuim per maand — hele organisatie (vraag 2)</t>
+  </si>
+  <si>
+    <t>langdurig als % van maandverzuim</t>
+  </si>
+  <si>
+    <t>Verzuim % excl. langdurig</t>
+  </si>
+  <si>
+    <t>3. Verzuim naar soort (vraag 3)</t>
+  </si>
+  <si>
+    <t>% van totaal verzuim</t>
+  </si>
+  <si>
+    <t>Registratieregels</t>
+  </si>
+  <si>
+    <t>Unieke medewerkers</t>
+  </si>
+  <si>
+    <t>4. Verzuim % per afdeling per maand (vraag 5) — let op: 4 tot 6 medewerkers per afdeling</t>
+  </si>
+  <si>
+    <t>5. Aandachtspunten voor de trainer</t>
+  </si>
+  <si>
+    <t>Kolom G in blok 2</t>
+  </si>
+  <si>
+    <t>Het verzuim % éxclusief langdurig verzuim. December zakt van 10,9% naar 2,6% en oktober van 9,9% naar 2,2%: de “najaarspiek” is bijna volledig één of twee langdurige gevallen, geen seizoenseffect.</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>November staat op 3,4%, tussen oktober (9,9%) en december (10,9%). Wie alleen de top-6 maanden laat zien, ziet een aaneengesloten najaarspiek die er niet is. Laat altijd alle 12 maanden zien.</t>
+  </si>
+  <si>
+    <t>Kleine aantallen</t>
+  </si>
+  <si>
+    <t>Elke afdeling heeft 4 tot 6 medewerkers (kolom G in blok 1). Facilitair juni 30,5% en Administratie februari 29,6% zijn één persoon. Noem het aantal mensen, niet het percentage.</t>
+  </si>
+  <si>
+    <t>Langdurig verzuim</t>
+  </si>
+  <si>
+    <t>55,4% van alle verzuimuren komt van 9 medewerkers. Een hoog afdelingspercentage zegt daarom weinig over de hele afdeling.</t>
+  </si>
+  <si>
+    <t>ICT heeft veel overuren (118) en het laagste verzuim (2,0%); Klantcontact heeft veel van beide. Geen één-op-één verband. Bovendien maakt wie langdurig ziek is per definitie geen overuren, wat elk verband mechanisch dempt.</t>
+  </si>
+  <si>
+    <t>Altijd benoemen</t>
+  </si>
+  <si>
+    <t>De data zijn verzonnen. Elk patroon hierboven is een oefening in kijken en doorvragen, geen uitspraak over echte mensen.</t>
+  </si>
+  <si>
+    <t>Antwoordmodel</t>
+  </si>
+  <si>
+    <t>Voor de trainer</t>
+  </si>
+  <si>
+    <t>Dit bestand bevat een verborgen tabblad 'Antwoordmodel' met de uitwerking van de zes vragen. Het wachtwoord is op te vragen bij de trainer.</t>
+  </si>
+  <si>
+    <t>Zichtbaar maken</t>
+  </si>
+  <si>
+    <t>Windows: rechtermuisklik op een tabblad onderaan &gt; Zichtbaar maken &gt; kies 'Antwoordmodel'. Mac: rechtermuisklik op een tabblad &gt; Zichtbaar maken. Lukt dat niet, dan zit er nog werkmapbeveiliging op: Controleren &gt; Werkmap beveiligen, wachtwoord invoeren, en daarna zichtbaar maken.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="mmm/yyyy"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="mmm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -380,13 +497,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -401,10 +532,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -428,6 +560,20 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -833,7 +979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86EAF557-6200-FC4E-A246-EED988E3F6F7}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -841,253 +987,276 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="24" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="4"/>
+      <c r="B1" s="5"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="5"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="5"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="5"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" s="5"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
     </row>
     <row r="8" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" s="5"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="A9" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
     </row>
     <row r="21" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="4"/>
+      <c r="B21" s="5"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
     </row>
     <row r="26" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="4"/>
+      <c r="B26" s="5"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="8">
+      <c r="A27" s="9">
         <v>1</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="8">
+      <c r="A28" s="9">
         <v>2</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="8">
+      <c r="A29" s="9">
         <v>3</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="8">
+      <c r="A30" s="9">
         <v>4</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="8">
+      <c r="A31" s="9">
         <v>5</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="5" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="4">
+      <c r="A32" s="5">
         <v>6</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
     </row>
     <row r="34" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="4"/>
+      <c r="B34" s="5"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B35" s="9"/>
+      <c r="B35" s="10"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B36" s="9"/>
+      <c r="B36" s="10"/>
+    </row>
+    <row r="38" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A38" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" s="5"/>
+    </row>
+    <row r="39" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A40" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>124</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -1145,7 +1314,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="10">
+      <c r="A2" s="11">
         <v>45658</v>
       </c>
       <c r="B2" t="s">
@@ -1175,13 +1344,13 @@
       <c r="J2" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="12">
         <f>IFERROR(H2/E2,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="10">
+      <c r="A3" s="11">
         <v>45658</v>
       </c>
       <c r="B3" t="s">
@@ -1211,13 +1380,13 @@
       <c r="J3" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="12">
         <f t="shared" ref="K3:K66" si="0">IFERROR(H3/E3,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="10">
+      <c r="A4" s="11">
         <v>45658</v>
       </c>
       <c r="B4" t="s">
@@ -1247,13 +1416,13 @@
       <c r="J4" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="12">
         <f t="shared" si="0"/>
         <v>4.716981132075472E-2</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="10">
+      <c r="A5" s="11">
         <v>45658</v>
       </c>
       <c r="B5" t="s">
@@ -1283,13 +1452,13 @@
       <c r="J5" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="10">
+      <c r="A6" s="11">
         <v>45658</v>
       </c>
       <c r="B6" t="s">
@@ -1319,13 +1488,13 @@
       <c r="J6" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="10">
+      <c r="A7" s="11">
         <v>45658</v>
       </c>
       <c r="B7" t="s">
@@ -1355,13 +1524,13 @@
       <c r="J7" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="10">
+      <c r="A8" s="11">
         <v>45658</v>
       </c>
       <c r="B8" t="s">
@@ -1391,13 +1560,13 @@
       <c r="J8" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="10">
+      <c r="A9" s="11">
         <v>45658</v>
       </c>
       <c r="B9" t="s">
@@ -1427,13 +1596,13 @@
       <c r="J9" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="12">
         <f t="shared" si="0"/>
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="10">
+      <c r="A10" s="11">
         <v>45658</v>
       </c>
       <c r="B10" t="s">
@@ -1463,13 +1632,13 @@
       <c r="J10" t="s">
         <v>18</v>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="12">
         <f t="shared" si="0"/>
         <v>9.2198581560283682E-2</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="10">
+      <c r="A11" s="11">
         <v>45658</v>
       </c>
       <c r="B11" t="s">
@@ -1499,13 +1668,13 @@
       <c r="J11" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="11">
+      <c r="K11" s="12">
         <f t="shared" si="0"/>
         <v>8.9820359281437126E-2</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="10">
+      <c r="A12" s="11">
         <v>45658</v>
       </c>
       <c r="B12" t="s">
@@ -1535,13 +1704,13 @@
       <c r="J12" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="12">
         <f t="shared" si="0"/>
         <v>9.2198581560283682E-2</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="10">
+      <c r="A13" s="11">
         <v>45658</v>
       </c>
       <c r="B13" t="s">
@@ -1571,13 +1740,13 @@
       <c r="J13" t="s">
         <v>14</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="10">
+      <c r="A14" s="11">
         <v>45658</v>
       </c>
       <c r="B14" t="s">
@@ -1607,13 +1776,13 @@
       <c r="J14" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="10">
+      <c r="A15" s="11">
         <v>45658</v>
       </c>
       <c r="B15" t="s">
@@ -1643,13 +1812,13 @@
       <c r="J15" t="s">
         <v>38</v>
       </c>
-      <c r="K15" s="11">
+      <c r="K15" s="12">
         <f t="shared" si="0"/>
         <v>0.41139240506329117</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="10">
+      <c r="A16" s="11">
         <v>45658</v>
       </c>
       <c r="B16" t="s">
@@ -1679,13 +1848,13 @@
       <c r="J16" t="s">
         <v>14</v>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="10">
+      <c r="A17" s="11">
         <v>45658</v>
       </c>
       <c r="B17" t="s">
@@ -1715,13 +1884,13 @@
       <c r="J17" t="s">
         <v>18</v>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="12">
         <f t="shared" si="0"/>
         <v>8.8607594936708861E-2</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="10">
+      <c r="A18" s="11">
         <v>45658</v>
       </c>
       <c r="B18" t="s">
@@ -1751,13 +1920,13 @@
       <c r="J18" t="s">
         <v>18</v>
       </c>
-      <c r="K18" s="11">
+      <c r="K18" s="12">
         <f t="shared" si="0"/>
         <v>4.2553191489361701E-2</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="10">
+      <c r="A19" s="11">
         <v>45658</v>
       </c>
       <c r="B19" t="s">
@@ -1787,13 +1956,13 @@
       <c r="J19" t="s">
         <v>14</v>
       </c>
-      <c r="K19" s="11">
+      <c r="K19" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="10">
+      <c r="A20" s="11">
         <v>45658</v>
       </c>
       <c r="B20" t="s">
@@ -1823,13 +1992,13 @@
       <c r="J20" t="s">
         <v>14</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="10">
+      <c r="A21" s="11">
         <v>45658</v>
       </c>
       <c r="B21" t="s">
@@ -1859,13 +2028,13 @@
       <c r="J21" t="s">
         <v>14</v>
       </c>
-      <c r="K21" s="11">
+      <c r="K21" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="10">
+      <c r="A22" s="11">
         <v>45658</v>
       </c>
       <c r="B22" t="s">
@@ -1895,13 +2064,13 @@
       <c r="J22" t="s">
         <v>14</v>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="10">
+      <c r="A23" s="11">
         <v>45658</v>
       </c>
       <c r="B23" t="s">
@@ -1931,13 +2100,13 @@
       <c r="J23" t="s">
         <v>14</v>
       </c>
-      <c r="K23" s="11">
+      <c r="K23" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="10">
+      <c r="A24" s="11">
         <v>45658</v>
       </c>
       <c r="B24" t="s">
@@ -1967,13 +2136,13 @@
       <c r="J24" t="s">
         <v>14</v>
       </c>
-      <c r="K24" s="11">
+      <c r="K24" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="10">
+      <c r="A25" s="11">
         <v>45658</v>
       </c>
       <c r="B25" t="s">
@@ -2003,13 +2172,13 @@
       <c r="J25" t="s">
         <v>14</v>
       </c>
-      <c r="K25" s="11">
+      <c r="K25" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="10">
+      <c r="A26" s="11">
         <v>45689</v>
       </c>
       <c r="B26" t="s">
@@ -2039,13 +2208,13 @@
       <c r="J26" t="s">
         <v>18</v>
       </c>
-      <c r="K26" s="11">
+      <c r="K26" s="12">
         <f t="shared" si="0"/>
         <v>4.6875E-2</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="10">
+      <c r="A27" s="11">
         <v>45689</v>
       </c>
       <c r="B27" t="s">
@@ -2075,13 +2244,13 @@
       <c r="J27" t="s">
         <v>18</v>
       </c>
-      <c r="K27" s="11">
+      <c r="K27" s="12">
         <f t="shared" si="0"/>
         <v>4.8611111111111112E-2</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="10">
+      <c r="A28" s="11">
         <v>45689</v>
       </c>
       <c r="B28" t="s">
@@ -2111,13 +2280,13 @@
       <c r="J28" t="s">
         <v>14</v>
       </c>
-      <c r="K28" s="11">
+      <c r="K28" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="10">
+      <c r="A29" s="11">
         <v>45689</v>
       </c>
       <c r="B29" t="s">
@@ -2147,13 +2316,13 @@
       <c r="J29" t="s">
         <v>18</v>
       </c>
-      <c r="K29" s="11">
+      <c r="K29" s="12">
         <f t="shared" si="0"/>
         <v>4.8611111111111112E-2</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="10">
+      <c r="A30" s="11">
         <v>45689</v>
       </c>
       <c r="B30" t="s">
@@ -2183,13 +2352,13 @@
       <c r="J30" t="s">
         <v>18</v>
       </c>
-      <c r="K30" s="11">
+      <c r="K30" s="12">
         <f t="shared" si="0"/>
         <v>0.15178571428571427</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="10">
+      <c r="A31" s="11">
         <v>45689</v>
       </c>
       <c r="B31" t="s">
@@ -2219,13 +2388,13 @@
       <c r="J31" t="s">
         <v>18</v>
       </c>
-      <c r="K31" s="11">
+      <c r="K31" s="12">
         <f t="shared" si="0"/>
         <v>9.7222222222222224E-2</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="10">
+      <c r="A32" s="11">
         <v>45689</v>
       </c>
       <c r="B32" t="s">
@@ -2255,13 +2424,13 @@
       <c r="J32" t="s">
         <v>14</v>
       </c>
-      <c r="K32" s="11">
+      <c r="K32" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" s="10">
+      <c r="A33" s="11">
         <v>45689</v>
       </c>
       <c r="B33" t="s">
@@ -2291,13 +2460,13 @@
       <c r="J33" t="s">
         <v>18</v>
       </c>
-      <c r="K33" s="11">
+      <c r="K33" s="12">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="10">
+      <c r="A34" s="11">
         <v>45689</v>
       </c>
       <c r="B34" t="s">
@@ -2327,13 +2496,13 @@
       <c r="J34" t="s">
         <v>14</v>
       </c>
-      <c r="K34" s="11">
+      <c r="K34" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="10">
+      <c r="A35" s="11">
         <v>45689</v>
       </c>
       <c r="B35" t="s">
@@ -2363,13 +2532,13 @@
       <c r="J35" t="s">
         <v>18</v>
       </c>
-      <c r="K35" s="11">
+      <c r="K35" s="12">
         <f t="shared" si="0"/>
         <v>5.2631578947368418E-2</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="10">
+      <c r="A36" s="11">
         <v>45689</v>
       </c>
       <c r="B36" t="s">
@@ -2399,13 +2568,13 @@
       <c r="J36" t="s">
         <v>14</v>
       </c>
-      <c r="K36" s="11">
+      <c r="K36" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="10">
+      <c r="A37" s="11">
         <v>45689</v>
       </c>
       <c r="B37" t="s">
@@ -2435,13 +2604,13 @@
       <c r="J37" t="s">
         <v>14</v>
       </c>
-      <c r="K37" s="11">
+      <c r="K37" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="10">
+      <c r="A38" s="11">
         <v>45689</v>
       </c>
       <c r="B38" t="s">
@@ -2471,13 +2640,13 @@
       <c r="J38" t="s">
         <v>38</v>
       </c>
-      <c r="K38" s="11">
+      <c r="K38" s="12">
         <f t="shared" si="0"/>
         <v>0.39583333333333331</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="10">
+      <c r="A39" s="11">
         <v>45689</v>
       </c>
       <c r="B39" t="s">
@@ -2507,13 +2676,13 @@
       <c r="J39" t="s">
         <v>14</v>
       </c>
-      <c r="K39" s="11">
+      <c r="K39" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="10">
+      <c r="A40" s="11">
         <v>45689</v>
       </c>
       <c r="B40" t="s">
@@ -2543,13 +2712,13 @@
       <c r="J40" t="s">
         <v>14</v>
       </c>
-      <c r="K40" s="11">
+      <c r="K40" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="10">
+      <c r="A41" s="11">
         <v>45689</v>
       </c>
       <c r="B41" t="s">
@@ -2579,13 +2748,13 @@
       <c r="J41" t="s">
         <v>14</v>
       </c>
-      <c r="K41" s="11">
+      <c r="K41" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="10">
+      <c r="A42" s="11">
         <v>45689</v>
       </c>
       <c r="B42" t="s">
@@ -2615,13 +2784,13 @@
       <c r="J42" t="s">
         <v>14</v>
       </c>
-      <c r="K42" s="11">
+      <c r="K42" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="10">
+      <c r="A43" s="11">
         <v>45689</v>
       </c>
       <c r="B43" t="s">
@@ -2651,13 +2820,13 @@
       <c r="J43" t="s">
         <v>59</v>
       </c>
-      <c r="K43" s="11">
+      <c r="K43" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="10">
+      <c r="A44" s="11">
         <v>45689</v>
       </c>
       <c r="B44" t="s">
@@ -2687,13 +2856,13 @@
       <c r="J44" t="s">
         <v>38</v>
       </c>
-      <c r="K44" s="11">
+      <c r="K44" s="12">
         <f t="shared" si="0"/>
         <v>0.3984375</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="10">
+      <c r="A45" s="11">
         <v>45689</v>
       </c>
       <c r="B45" t="s">
@@ -2723,13 +2892,13 @@
       <c r="J45" t="s">
         <v>14</v>
       </c>
-      <c r="K45" s="11">
+      <c r="K45" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="10">
+      <c r="A46" s="11">
         <v>45689</v>
       </c>
       <c r="B46" t="s">
@@ -2759,13 +2928,13 @@
       <c r="J46" t="s">
         <v>14</v>
       </c>
-      <c r="K46" s="11">
+      <c r="K46" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="10">
+      <c r="A47" s="11">
         <v>45689</v>
       </c>
       <c r="B47" t="s">
@@ -2795,13 +2964,13 @@
       <c r="J47" t="s">
         <v>14</v>
       </c>
-      <c r="K47" s="11">
+      <c r="K47" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="10">
+      <c r="A48" s="11">
         <v>45689</v>
       </c>
       <c r="B48" t="s">
@@ -2831,13 +3000,13 @@
       <c r="J48" t="s">
         <v>14</v>
       </c>
-      <c r="K48" s="11">
+      <c r="K48" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" s="10">
+      <c r="A49" s="11">
         <v>45689</v>
       </c>
       <c r="B49" t="s">
@@ -2867,13 +3036,13 @@
       <c r="J49" t="s">
         <v>14</v>
       </c>
-      <c r="K49" s="11">
+      <c r="K49" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="10">
+      <c r="A50" s="11">
         <v>45717</v>
       </c>
       <c r="B50" t="s">
@@ -2903,13 +3072,13 @@
       <c r="J50" t="s">
         <v>14</v>
       </c>
-      <c r="K50" s="11">
+      <c r="K50" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="10">
+      <c r="A51" s="11">
         <v>45717</v>
       </c>
       <c r="B51" t="s">
@@ -2939,13 +3108,13 @@
       <c r="J51" t="s">
         <v>14</v>
       </c>
-      <c r="K51" s="11">
+      <c r="K51" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="10">
+      <c r="A52" s="11">
         <v>45717</v>
       </c>
       <c r="B52" t="s">
@@ -2975,13 +3144,13 @@
       <c r="J52" t="s">
         <v>18</v>
       </c>
-      <c r="K52" s="11">
+      <c r="K52" s="12">
         <f t="shared" si="0"/>
         <v>4.716981132075472E-2</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="10">
+      <c r="A53" s="11">
         <v>45717</v>
       </c>
       <c r="B53" t="s">
@@ -3011,13 +3180,13 @@
       <c r="J53" t="s">
         <v>18</v>
       </c>
-      <c r="K53" s="11">
+      <c r="K53" s="12">
         <f t="shared" si="0"/>
         <v>8.8607594936708861E-2</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A54" s="10">
+      <c r="A54" s="11">
         <v>45717</v>
       </c>
       <c r="B54" t="s">
@@ -3047,13 +3216,13 @@
       <c r="J54" t="s">
         <v>14</v>
       </c>
-      <c r="K54" s="11">
+      <c r="K54" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A55" s="10">
+      <c r="A55" s="11">
         <v>45717</v>
       </c>
       <c r="B55" t="s">
@@ -3083,13 +3252,13 @@
       <c r="J55" t="s">
         <v>14</v>
       </c>
-      <c r="K55" s="11">
+      <c r="K55" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A56" s="10">
+      <c r="A56" s="11">
         <v>45717</v>
       </c>
       <c r="B56" t="s">
@@ -3119,13 +3288,13 @@
       <c r="J56" t="s">
         <v>14</v>
       </c>
-      <c r="K56" s="11">
+      <c r="K56" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" s="10">
+      <c r="A57" s="11">
         <v>45717</v>
       </c>
       <c r="B57" t="s">
@@ -3155,13 +3324,13 @@
       <c r="J57" t="s">
         <v>14</v>
       </c>
-      <c r="K57" s="11">
+      <c r="K57" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A58" s="10">
+      <c r="A58" s="11">
         <v>45717</v>
       </c>
       <c r="B58" t="s">
@@ -3191,13 +3360,13 @@
       <c r="J58" t="s">
         <v>14</v>
       </c>
-      <c r="K58" s="11">
+      <c r="K58" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A59" s="10">
+      <c r="A59" s="11">
         <v>45717</v>
       </c>
       <c r="B59" t="s">
@@ -3227,13 +3396,13 @@
       <c r="J59" t="s">
         <v>14</v>
       </c>
-      <c r="K59" s="11">
+      <c r="K59" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A60" s="10">
+      <c r="A60" s="11">
         <v>45717</v>
       </c>
       <c r="B60" t="s">
@@ -3263,13 +3432,13 @@
       <c r="J60" t="s">
         <v>14</v>
       </c>
-      <c r="K60" s="11">
+      <c r="K60" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A61" s="10">
+      <c r="A61" s="11">
         <v>45717</v>
       </c>
       <c r="B61" t="s">
@@ -3299,13 +3468,13 @@
       <c r="J61" t="s">
         <v>14</v>
       </c>
-      <c r="K61" s="11">
+      <c r="K61" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" s="10">
+      <c r="A62" s="11">
         <v>45717</v>
       </c>
       <c r="B62" t="s">
@@ -3335,13 +3504,13 @@
       <c r="J62" t="s">
         <v>18</v>
       </c>
-      <c r="K62" s="11">
+      <c r="K62" s="12">
         <f t="shared" si="0"/>
         <v>9.4339622641509441E-2</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A63" s="10">
+      <c r="A63" s="11">
         <v>45717</v>
       </c>
       <c r="B63" t="s">
@@ -3371,13 +3540,13 @@
       <c r="J63" t="s">
         <v>18</v>
       </c>
-      <c r="K63" s="11">
+      <c r="K63" s="12">
         <f t="shared" si="0"/>
         <v>0.13924050632911392</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A64" s="10">
+      <c r="A64" s="11">
         <v>45717</v>
       </c>
       <c r="B64" t="s">
@@ -3407,13 +3576,13 @@
       <c r="J64" t="s">
         <v>14</v>
       </c>
-      <c r="K64" s="11">
+      <c r="K64" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A65" s="10">
+      <c r="A65" s="11">
         <v>45717</v>
       </c>
       <c r="B65" t="s">
@@ -3443,13 +3612,13 @@
       <c r="J65" t="s">
         <v>14</v>
       </c>
-      <c r="K65" s="11">
+      <c r="K65" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A66" s="10">
+      <c r="A66" s="11">
         <v>45717</v>
       </c>
       <c r="B66" t="s">
@@ -3479,13 +3648,13 @@
       <c r="J66" t="s">
         <v>14</v>
       </c>
-      <c r="K66" s="11">
+      <c r="K66" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A67" s="10">
+      <c r="A67" s="11">
         <v>45717</v>
       </c>
       <c r="B67" t="s">
@@ -3515,13 +3684,13 @@
       <c r="J67" t="s">
         <v>14</v>
       </c>
-      <c r="K67" s="11">
+      <c r="K67" s="12">
         <f t="shared" ref="K67:K130" si="1">IFERROR(H67/E67,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A68" s="10">
+      <c r="A68" s="11">
         <v>45717</v>
       </c>
       <c r="B68" t="s">
@@ -3551,13 +3720,13 @@
       <c r="J68" t="s">
         <v>14</v>
       </c>
-      <c r="K68" s="11">
+      <c r="K68" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A69" s="10">
+      <c r="A69" s="11">
         <v>45717</v>
       </c>
       <c r="B69" t="s">
@@ -3587,13 +3756,13 @@
       <c r="J69" t="s">
         <v>14</v>
       </c>
-      <c r="K69" s="11">
+      <c r="K69" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A70" s="10">
+      <c r="A70" s="11">
         <v>45717</v>
       </c>
       <c r="B70" t="s">
@@ -3623,13 +3792,13 @@
       <c r="J70" t="s">
         <v>14</v>
       </c>
-      <c r="K70" s="11">
+      <c r="K70" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A71" s="10">
+      <c r="A71" s="11">
         <v>45717</v>
       </c>
       <c r="B71" t="s">
@@ -3659,13 +3828,13 @@
       <c r="J71" t="s">
         <v>14</v>
       </c>
-      <c r="K71" s="11">
+      <c r="K71" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A72" s="10">
+      <c r="A72" s="11">
         <v>45717</v>
       </c>
       <c r="B72" t="s">
@@ -3695,13 +3864,13 @@
       <c r="J72" t="s">
         <v>14</v>
       </c>
-      <c r="K72" s="11">
+      <c r="K72" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A73" s="10">
+      <c r="A73" s="11">
         <v>45717</v>
       </c>
       <c r="B73" t="s">
@@ -3731,13 +3900,13 @@
       <c r="J73" t="s">
         <v>14</v>
       </c>
-      <c r="K73" s="11">
+      <c r="K73" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A74" s="10">
+      <c r="A74" s="11">
         <v>45748</v>
       </c>
       <c r="B74" t="s">
@@ -3767,13 +3936,13 @@
       <c r="J74" t="s">
         <v>14</v>
       </c>
-      <c r="K74" s="11">
+      <c r="K74" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A75" s="10">
+      <c r="A75" s="11">
         <v>45748</v>
       </c>
       <c r="B75" t="s">
@@ -3803,13 +3972,13 @@
       <c r="J75" t="s">
         <v>14</v>
       </c>
-      <c r="K75" s="11">
+      <c r="K75" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A76" s="10">
+      <c r="A76" s="11">
         <v>45748</v>
       </c>
       <c r="B76" t="s">
@@ -3839,13 +4008,13 @@
       <c r="J76" t="s">
         <v>18</v>
       </c>
-      <c r="K76" s="11">
+      <c r="K76" s="12">
         <f t="shared" si="1"/>
         <v>0.10416666666666667</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A77" s="10">
+      <c r="A77" s="11">
         <v>45748</v>
       </c>
       <c r="B77" t="s">
@@ -3875,13 +4044,13 @@
       <c r="J77" t="s">
         <v>14</v>
       </c>
-      <c r="K77" s="11">
+      <c r="K77" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A78" s="10">
+      <c r="A78" s="11">
         <v>45748</v>
       </c>
       <c r="B78" t="s">
@@ -3911,13 +4080,13 @@
       <c r="J78" t="s">
         <v>14</v>
       </c>
-      <c r="K78" s="11">
+      <c r="K78" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A79" s="10">
+      <c r="A79" s="11">
         <v>45748</v>
       </c>
       <c r="B79" t="s">
@@ -3947,13 +4116,13 @@
       <c r="J79" t="s">
         <v>14</v>
       </c>
-      <c r="K79" s="11">
+      <c r="K79" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A80" s="10">
+      <c r="A80" s="11">
         <v>45748</v>
       </c>
       <c r="B80" t="s">
@@ -3983,13 +4152,13 @@
       <c r="J80" t="s">
         <v>14</v>
       </c>
-      <c r="K80" s="11">
+      <c r="K80" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A81" s="10">
+      <c r="A81" s="11">
         <v>45748</v>
       </c>
       <c r="B81" t="s">
@@ -4019,13 +4188,13 @@
       <c r="J81" t="s">
         <v>14</v>
       </c>
-      <c r="K81" s="11">
+      <c r="K81" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A82" s="10">
+      <c r="A82" s="11">
         <v>45748</v>
       </c>
       <c r="B82" t="s">
@@ -4055,13 +4224,13 @@
       <c r="J82" t="s">
         <v>14</v>
       </c>
-      <c r="K82" s="11">
+      <c r="K82" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A83" s="10">
+      <c r="A83" s="11">
         <v>45748</v>
       </c>
       <c r="B83" t="s">
@@ -4091,13 +4260,13 @@
       <c r="J83" t="s">
         <v>14</v>
       </c>
-      <c r="K83" s="11">
+      <c r="K83" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A84" s="10">
+      <c r="A84" s="11">
         <v>45748</v>
       </c>
       <c r="B84" t="s">
@@ -4127,13 +4296,13 @@
       <c r="J84" t="s">
         <v>14</v>
       </c>
-      <c r="K84" s="11">
+      <c r="K84" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A85" s="10">
+      <c r="A85" s="11">
         <v>45748</v>
       </c>
       <c r="B85" t="s">
@@ -4163,13 +4332,13 @@
       <c r="J85" t="s">
         <v>14</v>
       </c>
-      <c r="K85" s="11">
+      <c r="K85" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A86" s="10">
+      <c r="A86" s="11">
         <v>45748</v>
       </c>
       <c r="B86" t="s">
@@ -4199,13 +4368,13 @@
       <c r="J86" t="s">
         <v>14</v>
       </c>
-      <c r="K86" s="11">
+      <c r="K86" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A87" s="10">
+      <c r="A87" s="11">
         <v>45748</v>
       </c>
       <c r="B87" t="s">
@@ -4235,13 +4404,13 @@
       <c r="J87" t="s">
         <v>14</v>
       </c>
-      <c r="K87" s="11">
+      <c r="K87" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A88" s="10">
+      <c r="A88" s="11">
         <v>45748</v>
       </c>
       <c r="B88" t="s">
@@ -4271,13 +4440,13 @@
       <c r="J88" t="s">
         <v>18</v>
       </c>
-      <c r="K88" s="11">
+      <c r="K88" s="12">
         <f t="shared" si="1"/>
         <v>5.3571428571428568E-2</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A89" s="10">
+      <c r="A89" s="11">
         <v>45748</v>
       </c>
       <c r="B89" t="s">
@@ -4307,13 +4476,13 @@
       <c r="J89" t="s">
         <v>14</v>
       </c>
-      <c r="K89" s="11">
+      <c r="K89" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A90" s="10">
+      <c r="A90" s="11">
         <v>45748</v>
       </c>
       <c r="B90" t="s">
@@ -4343,13 +4512,13 @@
       <c r="J90" t="s">
         <v>14</v>
       </c>
-      <c r="K90" s="11">
+      <c r="K90" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A91" s="10">
+      <c r="A91" s="11">
         <v>45748</v>
       </c>
       <c r="B91" t="s">
@@ -4379,13 +4548,13 @@
       <c r="J91" t="s">
         <v>14</v>
       </c>
-      <c r="K91" s="11">
+      <c r="K91" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A92" s="10">
+      <c r="A92" s="11">
         <v>45748</v>
       </c>
       <c r="B92" t="s">
@@ -4415,13 +4584,13 @@
       <c r="J92" t="s">
         <v>14</v>
       </c>
-      <c r="K92" s="11">
+      <c r="K92" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A93" s="10">
+      <c r="A93" s="11">
         <v>45748</v>
       </c>
       <c r="B93" t="s">
@@ -4451,13 +4620,13 @@
       <c r="J93" t="s">
         <v>14</v>
       </c>
-      <c r="K93" s="11">
+      <c r="K93" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A94" s="10">
+      <c r="A94" s="11">
         <v>45748</v>
       </c>
       <c r="B94" t="s">
@@ -4487,13 +4656,13 @@
       <c r="J94" t="s">
         <v>14</v>
       </c>
-      <c r="K94" s="11">
+      <c r="K94" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A95" s="10">
+      <c r="A95" s="11">
         <v>45748</v>
       </c>
       <c r="B95" t="s">
@@ -4523,13 +4692,13 @@
       <c r="J95" t="s">
         <v>14</v>
       </c>
-      <c r="K95" s="11">
+      <c r="K95" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A96" s="10">
+      <c r="A96" s="11">
         <v>45748</v>
       </c>
       <c r="B96" t="s">
@@ -4559,13 +4728,13 @@
       <c r="J96" t="s">
         <v>14</v>
       </c>
-      <c r="K96" s="11">
+      <c r="K96" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A97" s="10">
+      <c r="A97" s="11">
         <v>45748</v>
       </c>
       <c r="B97" t="s">
@@ -4595,13 +4764,13 @@
       <c r="J97" t="s">
         <v>14</v>
       </c>
-      <c r="K97" s="11">
+      <c r="K97" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A98" s="10">
+      <c r="A98" s="11">
         <v>45778</v>
       </c>
       <c r="B98" t="s">
@@ -4631,13 +4800,13 @@
       <c r="J98" t="s">
         <v>14</v>
       </c>
-      <c r="K98" s="11">
+      <c r="K98" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A99" s="10">
+      <c r="A99" s="11">
         <v>45778</v>
       </c>
       <c r="B99" t="s">
@@ -4667,13 +4836,13 @@
       <c r="J99" t="s">
         <v>14</v>
       </c>
-      <c r="K99" s="11">
+      <c r="K99" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A100" s="10">
+      <c r="A100" s="11">
         <v>45778</v>
       </c>
       <c r="B100" t="s">
@@ -4703,13 +4872,13 @@
       <c r="J100" t="s">
         <v>14</v>
       </c>
-      <c r="K100" s="11">
+      <c r="K100" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A101" s="10">
+      <c r="A101" s="11">
         <v>45778</v>
       </c>
       <c r="B101" t="s">
@@ -4739,13 +4908,13 @@
       <c r="J101" t="s">
         <v>59</v>
       </c>
-      <c r="K101" s="11">
+      <c r="K101" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A102" s="10">
+      <c r="A102" s="11">
         <v>45778</v>
       </c>
       <c r="B102" t="s">
@@ -4775,13 +4944,13 @@
       <c r="J102" t="s">
         <v>14</v>
       </c>
-      <c r="K102" s="11">
+      <c r="K102" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A103" s="10">
+      <c r="A103" s="11">
         <v>45778</v>
       </c>
       <c r="B103" t="s">
@@ -4811,13 +4980,13 @@
       <c r="J103" t="s">
         <v>14</v>
       </c>
-      <c r="K103" s="11">
+      <c r="K103" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A104" s="10">
+      <c r="A104" s="11">
         <v>45778</v>
       </c>
       <c r="B104" t="s">
@@ -4847,13 +5016,13 @@
       <c r="J104" t="s">
         <v>14</v>
       </c>
-      <c r="K104" s="11">
+      <c r="K104" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A105" s="10">
+      <c r="A105" s="11">
         <v>45778</v>
       </c>
       <c r="B105" t="s">
@@ -4883,13 +5052,13 @@
       <c r="J105" t="s">
         <v>14</v>
       </c>
-      <c r="K105" s="11">
+      <c r="K105" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A106" s="10">
+      <c r="A106" s="11">
         <v>45778</v>
       </c>
       <c r="B106" t="s">
@@ -4919,13 +5088,13 @@
       <c r="J106" t="s">
         <v>14</v>
       </c>
-      <c r="K106" s="11">
+      <c r="K106" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A107" s="10">
+      <c r="A107" s="11">
         <v>45778</v>
       </c>
       <c r="B107" t="s">
@@ -4955,13 +5124,13 @@
       <c r="J107" t="s">
         <v>14</v>
       </c>
-      <c r="K107" s="11">
+      <c r="K107" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A108" s="10">
+      <c r="A108" s="11">
         <v>45778</v>
       </c>
       <c r="B108" t="s">
@@ -4991,13 +5160,13 @@
       <c r="J108" t="s">
         <v>14</v>
       </c>
-      <c r="K108" s="11">
+      <c r="K108" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A109" s="10">
+      <c r="A109" s="11">
         <v>45778</v>
       </c>
       <c r="B109" t="s">
@@ -5027,13 +5196,13 @@
       <c r="J109" t="s">
         <v>18</v>
       </c>
-      <c r="K109" s="11">
+      <c r="K109" s="12">
         <f t="shared" si="1"/>
         <v>4.6357615894039736E-2</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A110" s="10">
+      <c r="A110" s="11">
         <v>45778</v>
       </c>
       <c r="B110" t="s">
@@ -5063,13 +5232,13 @@
       <c r="J110" t="s">
         <v>14</v>
       </c>
-      <c r="K110" s="11">
+      <c r="K110" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A111" s="10">
+      <c r="A111" s="11">
         <v>45778</v>
       </c>
       <c r="B111" t="s">
@@ -5099,13 +5268,13 @@
       <c r="J111" t="s">
         <v>14</v>
       </c>
-      <c r="K111" s="11">
+      <c r="K111" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A112" s="10">
+      <c r="A112" s="11">
         <v>45778</v>
       </c>
       <c r="B112" t="s">
@@ -5135,13 +5304,13 @@
       <c r="J112" t="s">
         <v>14</v>
       </c>
-      <c r="K112" s="11">
+      <c r="K112" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A113" s="10">
+      <c r="A113" s="11">
         <v>45778</v>
       </c>
       <c r="B113" t="s">
@@ -5171,13 +5340,13 @@
       <c r="J113" t="s">
         <v>14</v>
       </c>
-      <c r="K113" s="11">
+      <c r="K113" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A114" s="10">
+      <c r="A114" s="11">
         <v>45778</v>
       </c>
       <c r="B114" t="s">
@@ -5207,13 +5376,13 @@
       <c r="J114" t="s">
         <v>14</v>
       </c>
-      <c r="K114" s="11">
+      <c r="K114" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A115" s="10">
+      <c r="A115" s="11">
         <v>45778</v>
       </c>
       <c r="B115" t="s">
@@ -5243,13 +5412,13 @@
       <c r="J115" t="s">
         <v>14</v>
       </c>
-      <c r="K115" s="11">
+      <c r="K115" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A116" s="10">
+      <c r="A116" s="11">
         <v>45778</v>
       </c>
       <c r="B116" t="s">
@@ -5279,13 +5448,13 @@
       <c r="J116" t="s">
         <v>38</v>
       </c>
-      <c r="K116" s="11">
+      <c r="K116" s="12">
         <f t="shared" si="1"/>
         <v>0.38059701492537312</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A117" s="10">
+      <c r="A117" s="11">
         <v>45778</v>
       </c>
       <c r="B117" t="s">
@@ -5315,13 +5484,13 @@
       <c r="J117" t="s">
         <v>14</v>
       </c>
-      <c r="K117" s="11">
+      <c r="K117" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A118" s="10">
+      <c r="A118" s="11">
         <v>45778</v>
       </c>
       <c r="B118" t="s">
@@ -5351,13 +5520,13 @@
       <c r="J118" t="s">
         <v>14</v>
       </c>
-      <c r="K118" s="11">
+      <c r="K118" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A119" s="10">
+      <c r="A119" s="11">
         <v>45778</v>
       </c>
       <c r="B119" t="s">
@@ -5387,13 +5556,13 @@
       <c r="J119" t="s">
         <v>14</v>
       </c>
-      <c r="K119" s="11">
+      <c r="K119" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A120" s="10">
+      <c r="A120" s="11">
         <v>45778</v>
       </c>
       <c r="B120" t="s">
@@ -5423,13 +5592,13 @@
       <c r="J120" t="s">
         <v>14</v>
       </c>
-      <c r="K120" s="11">
+      <c r="K120" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A121" s="10">
+      <c r="A121" s="11">
         <v>45778</v>
       </c>
       <c r="B121" t="s">
@@ -5459,13 +5628,13 @@
       <c r="J121" t="s">
         <v>14</v>
       </c>
-      <c r="K121" s="11">
+      <c r="K121" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A122" s="10">
+      <c r="A122" s="11">
         <v>45809</v>
       </c>
       <c r="B122" t="s">
@@ -5495,13 +5664,13 @@
       <c r="J122" t="s">
         <v>38</v>
       </c>
-      <c r="K122" s="11">
+      <c r="K122" s="12">
         <f t="shared" si="1"/>
         <v>0.57462686567164178</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A123" s="10">
+      <c r="A123" s="11">
         <v>45809</v>
       </c>
       <c r="B123" t="s">
@@ -5531,13 +5700,13 @@
       <c r="J123" t="s">
         <v>18</v>
       </c>
-      <c r="K123" s="11">
+      <c r="K123" s="12">
         <f t="shared" si="1"/>
         <v>9.2715231788079472E-2</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A124" s="10">
+      <c r="A124" s="11">
         <v>45809</v>
       </c>
       <c r="B124" t="s">
@@ -5567,13 +5736,13 @@
       <c r="J124" t="s">
         <v>14</v>
       </c>
-      <c r="K124" s="11">
+      <c r="K124" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A125" s="10">
+      <c r="A125" s="11">
         <v>45809</v>
       </c>
       <c r="B125" t="s">
@@ -5603,13 +5772,13 @@
       <c r="J125" t="s">
         <v>14</v>
       </c>
-      <c r="K125" s="11">
+      <c r="K125" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A126" s="10">
+      <c r="A126" s="11">
         <v>45809</v>
       </c>
       <c r="B126" t="s">
@@ -5639,13 +5808,13 @@
       <c r="J126" t="s">
         <v>14</v>
       </c>
-      <c r="K126" s="11">
+      <c r="K126" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A127" s="10">
+      <c r="A127" s="11">
         <v>45809</v>
       </c>
       <c r="B127" t="s">
@@ -5675,13 +5844,13 @@
       <c r="J127" t="s">
         <v>14</v>
       </c>
-      <c r="K127" s="11">
+      <c r="K127" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A128" s="10">
+      <c r="A128" s="11">
         <v>45809</v>
       </c>
       <c r="B128" t="s">
@@ -5711,13 +5880,13 @@
       <c r="J128" t="s">
         <v>14</v>
       </c>
-      <c r="K128" s="11">
+      <c r="K128" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A129" s="10">
+      <c r="A129" s="11">
         <v>45809</v>
       </c>
       <c r="B129" t="s">
@@ -5747,13 +5916,13 @@
       <c r="J129" t="s">
         <v>18</v>
       </c>
-      <c r="K129" s="11">
+      <c r="K129" s="12">
         <f t="shared" si="1"/>
         <v>4.7619047619047616E-2</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A130" s="10">
+      <c r="A130" s="11">
         <v>45809</v>
       </c>
       <c r="B130" t="s">
@@ -5783,13 +5952,13 @@
       <c r="J130" t="s">
         <v>14</v>
       </c>
-      <c r="K130" s="11">
+      <c r="K130" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A131" s="10">
+      <c r="A131" s="11">
         <v>45809</v>
       </c>
       <c r="B131" t="s">
@@ -5819,13 +5988,13 @@
       <c r="J131" t="s">
         <v>59</v>
       </c>
-      <c r="K131" s="11">
+      <c r="K131" s="12">
         <f t="shared" ref="K131:K194" si="2">IFERROR(H131/E131,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A132" s="10">
+      <c r="A132" s="11">
         <v>45809</v>
       </c>
       <c r="B132" t="s">
@@ -5855,13 +6024,13 @@
       <c r="J132" t="s">
         <v>14</v>
       </c>
-      <c r="K132" s="11">
+      <c r="K132" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A133" s="10">
+      <c r="A133" s="11">
         <v>45809</v>
       </c>
       <c r="B133" t="s">
@@ -5891,13 +6060,13 @@
       <c r="J133" t="s">
         <v>18</v>
       </c>
-      <c r="K133" s="11">
+      <c r="K133" s="12">
         <f t="shared" si="2"/>
         <v>0.14569536423841059</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A134" s="10">
+      <c r="A134" s="11">
         <v>45809</v>
       </c>
       <c r="B134" t="s">
@@ -5927,13 +6096,13 @@
       <c r="J134" t="s">
         <v>14</v>
       </c>
-      <c r="K134" s="11">
+      <c r="K134" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A135" s="10">
+      <c r="A135" s="11">
         <v>45809</v>
       </c>
       <c r="B135" t="s">
@@ -5963,13 +6132,13 @@
       <c r="J135" t="s">
         <v>14</v>
       </c>
-      <c r="K135" s="11">
+      <c r="K135" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A136" s="10">
+      <c r="A136" s="11">
         <v>45809</v>
       </c>
       <c r="B136" t="s">
@@ -5999,13 +6168,13 @@
       <c r="J136" t="s">
         <v>14</v>
       </c>
-      <c r="K136" s="11">
+      <c r="K136" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A137" s="10">
+      <c r="A137" s="11">
         <v>45809</v>
       </c>
       <c r="B137" t="s">
@@ -6035,13 +6204,13 @@
       <c r="J137" t="s">
         <v>14</v>
       </c>
-      <c r="K137" s="11">
+      <c r="K137" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A138" s="10">
+      <c r="A138" s="11">
         <v>45809</v>
       </c>
       <c r="B138" t="s">
@@ -6071,13 +6240,13 @@
       <c r="J138" t="s">
         <v>14</v>
       </c>
-      <c r="K138" s="11">
+      <c r="K138" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A139" s="10">
+      <c r="A139" s="11">
         <v>45809</v>
       </c>
       <c r="B139" t="s">
@@ -6107,13 +6276,13 @@
       <c r="J139" t="s">
         <v>14</v>
       </c>
-      <c r="K139" s="11">
+      <c r="K139" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A140" s="10">
+      <c r="A140" s="11">
         <v>45809</v>
       </c>
       <c r="B140" t="s">
@@ -6143,13 +6312,13 @@
       <c r="J140" t="s">
         <v>14</v>
       </c>
-      <c r="K140" s="11">
+      <c r="K140" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A141" s="10">
+      <c r="A141" s="11">
         <v>45809</v>
       </c>
       <c r="B141" t="s">
@@ -6179,13 +6348,13 @@
       <c r="J141" t="s">
         <v>14</v>
       </c>
-      <c r="K141" s="11">
+      <c r="K141" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A142" s="10">
+      <c r="A142" s="11">
         <v>45809</v>
       </c>
       <c r="B142" t="s">
@@ -6215,13 +6384,13 @@
       <c r="J142" t="s">
         <v>14</v>
       </c>
-      <c r="K142" s="11">
+      <c r="K142" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A143" s="10">
+      <c r="A143" s="11">
         <v>45809</v>
       </c>
       <c r="B143" t="s">
@@ -6251,13 +6420,13 @@
       <c r="J143" t="s">
         <v>14</v>
       </c>
-      <c r="K143" s="11">
+      <c r="K143" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A144" s="10">
+      <c r="A144" s="11">
         <v>45809</v>
       </c>
       <c r="B144" t="s">
@@ -6287,13 +6456,13 @@
       <c r="J144" t="s">
         <v>14</v>
       </c>
-      <c r="K144" s="11">
+      <c r="K144" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A145" s="10">
+      <c r="A145" s="11">
         <v>45809</v>
       </c>
       <c r="B145" t="s">
@@ -6323,13 +6492,13 @@
       <c r="J145" t="s">
         <v>14</v>
       </c>
-      <c r="K145" s="11">
+      <c r="K145" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A146" s="10">
+      <c r="A146" s="11">
         <v>45839</v>
       </c>
       <c r="B146" t="s">
@@ -6359,13 +6528,13 @@
       <c r="J146" t="s">
         <v>18</v>
       </c>
-      <c r="K146" s="11">
+      <c r="K146" s="12">
         <f t="shared" si="2"/>
         <v>9.2198581560283682E-2</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A147" s="10">
+      <c r="A147" s="11">
         <v>45839</v>
       </c>
       <c r="B147" t="s">
@@ -6395,13 +6564,13 @@
       <c r="J147" t="s">
         <v>59</v>
       </c>
-      <c r="K147" s="11">
+      <c r="K147" s="12">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A148" s="10">
+      <c r="A148" s="11">
         <v>45839</v>
       </c>
       <c r="B148" t="s">
@@ -6431,13 +6600,13 @@
       <c r="J148" t="s">
         <v>14</v>
       </c>
-      <c r="K148" s="11">
+      <c r="K148" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A149" s="10">
+      <c r="A149" s="11">
         <v>45839</v>
       </c>
       <c r="B149" t="s">
@@ -6467,13 +6636,13 @@
       <c r="J149" t="s">
         <v>14</v>
       </c>
-      <c r="K149" s="11">
+      <c r="K149" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A150" s="10">
+      <c r="A150" s="11">
         <v>45839</v>
       </c>
       <c r="B150" t="s">
@@ -6503,13 +6672,13 @@
       <c r="J150" t="s">
         <v>14</v>
       </c>
-      <c r="K150" s="11">
+      <c r="K150" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A151" s="10">
+      <c r="A151" s="11">
         <v>45839</v>
       </c>
       <c r="B151" t="s">
@@ -6539,13 +6708,13 @@
       <c r="J151" t="s">
         <v>14</v>
       </c>
-      <c r="K151" s="11">
+      <c r="K151" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A152" s="10">
+      <c r="A152" s="11">
         <v>45839</v>
       </c>
       <c r="B152" t="s">
@@ -6575,13 +6744,13 @@
       <c r="J152" t="s">
         <v>14</v>
       </c>
-      <c r="K152" s="11">
+      <c r="K152" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A153" s="10">
+      <c r="A153" s="11">
         <v>45839</v>
       </c>
       <c r="B153" t="s">
@@ -6611,13 +6780,13 @@
       <c r="J153" t="s">
         <v>14</v>
       </c>
-      <c r="K153" s="11">
+      <c r="K153" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A154" s="10">
+      <c r="A154" s="11">
         <v>45839</v>
       </c>
       <c r="B154" t="s">
@@ -6647,13 +6816,13 @@
       <c r="J154" t="s">
         <v>14</v>
       </c>
-      <c r="K154" s="11">
+      <c r="K154" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A155" s="10">
+      <c r="A155" s="11">
         <v>45839</v>
       </c>
       <c r="B155" t="s">
@@ -6683,13 +6852,13 @@
       <c r="J155" t="s">
         <v>18</v>
       </c>
-      <c r="K155" s="11">
+      <c r="K155" s="12">
         <f t="shared" si="2"/>
         <v>4.790419161676647E-2</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A156" s="10">
+      <c r="A156" s="11">
         <v>45839</v>
       </c>
       <c r="B156" t="s">
@@ -6719,13 +6888,13 @@
       <c r="J156" t="s">
         <v>14</v>
       </c>
-      <c r="K156" s="11">
+      <c r="K156" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A157" s="10">
+      <c r="A157" s="11">
         <v>45839</v>
       </c>
       <c r="B157" t="s">
@@ -6755,13 +6924,13 @@
       <c r="J157" t="s">
         <v>38</v>
       </c>
-      <c r="K157" s="11">
+      <c r="K157" s="12">
         <f t="shared" si="2"/>
         <v>0.36708860759493672</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A158" s="10">
+      <c r="A158" s="11">
         <v>45839</v>
       </c>
       <c r="B158" t="s">
@@ -6791,13 +6960,13 @@
       <c r="J158" t="s">
         <v>14</v>
       </c>
-      <c r="K158" s="11">
+      <c r="K158" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A159" s="10">
+      <c r="A159" s="11">
         <v>45839</v>
       </c>
       <c r="B159" t="s">
@@ -6827,13 +6996,13 @@
       <c r="J159" t="s">
         <v>14</v>
       </c>
-      <c r="K159" s="11">
+      <c r="K159" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A160" s="10">
+      <c r="A160" s="11">
         <v>45839</v>
       </c>
       <c r="B160" t="s">
@@ -6863,13 +7032,13 @@
       <c r="J160" t="s">
         <v>14</v>
       </c>
-      <c r="K160" s="11">
+      <c r="K160" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A161" s="10">
+      <c r="A161" s="11">
         <v>45839</v>
       </c>
       <c r="B161" t="s">
@@ -6899,13 +7068,13 @@
       <c r="J161" t="s">
         <v>14</v>
       </c>
-      <c r="K161" s="11">
+      <c r="K161" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A162" s="10">
+      <c r="A162" s="11">
         <v>45839</v>
       </c>
       <c r="B162" t="s">
@@ -6935,13 +7104,13 @@
       <c r="J162" t="s">
         <v>14</v>
       </c>
-      <c r="K162" s="11">
+      <c r="K162" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A163" s="10">
+      <c r="A163" s="11">
         <v>45839</v>
       </c>
       <c r="B163" t="s">
@@ -6971,13 +7140,13 @@
       <c r="J163" t="s">
         <v>14</v>
       </c>
-      <c r="K163" s="11">
+      <c r="K163" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A164" s="10">
+      <c r="A164" s="11">
         <v>45839</v>
       </c>
       <c r="B164" t="s">
@@ -7007,13 +7176,13 @@
       <c r="J164" t="s">
         <v>14</v>
       </c>
-      <c r="K164" s="11">
+      <c r="K164" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A165" s="10">
+      <c r="A165" s="11">
         <v>45839</v>
       </c>
       <c r="B165" t="s">
@@ -7043,13 +7212,13 @@
       <c r="J165" t="s">
         <v>14</v>
       </c>
-      <c r="K165" s="11">
+      <c r="K165" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A166" s="10">
+      <c r="A166" s="11">
         <v>45839</v>
       </c>
       <c r="B166" t="s">
@@ -7079,13 +7248,13 @@
       <c r="J166" t="s">
         <v>14</v>
       </c>
-      <c r="K166" s="11">
+      <c r="K166" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A167" s="10">
+      <c r="A167" s="11">
         <v>45839</v>
       </c>
       <c r="B167" t="s">
@@ -7115,13 +7284,13 @@
       <c r="J167" t="s">
         <v>14</v>
       </c>
-      <c r="K167" s="11">
+      <c r="K167" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A168" s="10">
+      <c r="A168" s="11">
         <v>45839</v>
       </c>
       <c r="B168" t="s">
@@ -7151,13 +7320,13 @@
       <c r="J168" t="s">
         <v>14</v>
       </c>
-      <c r="K168" s="11">
+      <c r="K168" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A169" s="10">
+      <c r="A169" s="11">
         <v>45839</v>
       </c>
       <c r="B169" t="s">
@@ -7187,13 +7356,13 @@
       <c r="J169" t="s">
         <v>14</v>
       </c>
-      <c r="K169" s="11">
+      <c r="K169" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A170" s="10">
+      <c r="A170" s="11">
         <v>45870</v>
       </c>
       <c r="B170" t="s">
@@ -7223,13 +7392,13 @@
       <c r="J170" t="s">
         <v>14</v>
       </c>
-      <c r="K170" s="11">
+      <c r="K170" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A171" s="10">
+      <c r="A171" s="11">
         <v>45870</v>
       </c>
       <c r="B171" t="s">
@@ -7259,13 +7428,13 @@
       <c r="J171" t="s">
         <v>14</v>
       </c>
-      <c r="K171" s="11">
+      <c r="K171" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A172" s="10">
+      <c r="A172" s="11">
         <v>45870</v>
       </c>
       <c r="B172" t="s">
@@ -7295,13 +7464,13 @@
       <c r="J172" t="s">
         <v>14</v>
       </c>
-      <c r="K172" s="11">
+      <c r="K172" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A173" s="10">
+      <c r="A173" s="11">
         <v>45870</v>
       </c>
       <c r="B173" t="s">
@@ -7331,13 +7500,13 @@
       <c r="J173" t="s">
         <v>14</v>
       </c>
-      <c r="K173" s="11">
+      <c r="K173" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A174" s="10">
+      <c r="A174" s="11">
         <v>45870</v>
       </c>
       <c r="B174" t="s">
@@ -7367,13 +7536,13 @@
       <c r="J174" t="s">
         <v>18</v>
       </c>
-      <c r="K174" s="11">
+      <c r="K174" s="12">
         <f t="shared" si="2"/>
         <v>0.1440677966101695</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A175" s="10">
+      <c r="A175" s="11">
         <v>45870</v>
       </c>
       <c r="B175" t="s">
@@ -7403,13 +7572,13 @@
       <c r="J175" t="s">
         <v>14</v>
       </c>
-      <c r="K175" s="11">
+      <c r="K175" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A176" s="10">
+      <c r="A176" s="11">
         <v>45870</v>
       </c>
       <c r="B176" t="s">
@@ -7439,13 +7608,13 @@
       <c r="J176" t="s">
         <v>14</v>
       </c>
-      <c r="K176" s="11">
+      <c r="K176" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A177" s="10">
+      <c r="A177" s="11">
         <v>45870</v>
       </c>
       <c r="B177" t="s">
@@ -7475,13 +7644,13 @@
       <c r="J177" t="s">
         <v>14</v>
       </c>
-      <c r="K177" s="11">
+      <c r="K177" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A178" s="10">
+      <c r="A178" s="11">
         <v>45870</v>
       </c>
       <c r="B178" t="s">
@@ -7511,13 +7680,13 @@
       <c r="J178" t="s">
         <v>14</v>
       </c>
-      <c r="K178" s="11">
+      <c r="K178" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A179" s="10">
+      <c r="A179" s="11">
         <v>45870</v>
       </c>
       <c r="B179" t="s">
@@ -7547,13 +7716,13 @@
       <c r="J179" t="s">
         <v>14</v>
       </c>
-      <c r="K179" s="11">
+      <c r="K179" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A180" s="10">
+      <c r="A180" s="11">
         <v>45870</v>
       </c>
       <c r="B180" t="s">
@@ -7583,13 +7752,13 @@
       <c r="J180" t="s">
         <v>14</v>
       </c>
-      <c r="K180" s="11">
+      <c r="K180" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A181" s="10">
+      <c r="A181" s="11">
         <v>45870</v>
       </c>
       <c r="B181" t="s">
@@ -7619,13 +7788,13 @@
       <c r="J181" t="s">
         <v>14</v>
       </c>
-      <c r="K181" s="11">
+      <c r="K181" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A182" s="10">
+      <c r="A182" s="11">
         <v>45870</v>
       </c>
       <c r="B182" t="s">
@@ -7655,13 +7824,13 @@
       <c r="J182" t="s">
         <v>14</v>
       </c>
-      <c r="K182" s="11">
+      <c r="K182" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A183" s="10">
+      <c r="A183" s="11">
         <v>45870</v>
       </c>
       <c r="B183" t="s">
@@ -7691,13 +7860,13 @@
       <c r="J183" t="s">
         <v>18</v>
       </c>
-      <c r="K183" s="11">
+      <c r="K183" s="12">
         <f t="shared" si="2"/>
         <v>0.14569536423841059</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A184" s="10">
+      <c r="A184" s="11">
         <v>45870</v>
       </c>
       <c r="B184" t="s">
@@ -7727,13 +7896,13 @@
       <c r="J184" t="s">
         <v>14</v>
       </c>
-      <c r="K184" s="11">
+      <c r="K184" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A185" s="10">
+      <c r="A185" s="11">
         <v>45870</v>
       </c>
       <c r="B185" t="s">
@@ -7763,13 +7932,13 @@
       <c r="J185" t="s">
         <v>14</v>
       </c>
-      <c r="K185" s="11">
+      <c r="K185" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A186" s="10">
+      <c r="A186" s="11">
         <v>45870</v>
       </c>
       <c r="B186" t="s">
@@ -7799,13 +7968,13 @@
       <c r="J186" t="s">
         <v>14</v>
       </c>
-      <c r="K186" s="11">
+      <c r="K186" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A187" s="10">
+      <c r="A187" s="11">
         <v>45870</v>
       </c>
       <c r="B187" t="s">
@@ -7835,13 +8004,13 @@
       <c r="J187" t="s">
         <v>14</v>
       </c>
-      <c r="K187" s="11">
+      <c r="K187" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A188" s="10">
+      <c r="A188" s="11">
         <v>45870</v>
       </c>
       <c r="B188" t="s">
@@ -7871,13 +8040,13 @@
       <c r="J188" t="s">
         <v>14</v>
       </c>
-      <c r="K188" s="11">
+      <c r="K188" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A189" s="10">
+      <c r="A189" s="11">
         <v>45870</v>
       </c>
       <c r="B189" t="s">
@@ -7907,13 +8076,13 @@
       <c r="J189" t="s">
         <v>14</v>
       </c>
-      <c r="K189" s="11">
+      <c r="K189" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A190" s="10">
+      <c r="A190" s="11">
         <v>45870</v>
       </c>
       <c r="B190" t="s">
@@ -7943,13 +8112,13 @@
       <c r="J190" t="s">
         <v>14</v>
       </c>
-      <c r="K190" s="11">
+      <c r="K190" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A191" s="10">
+      <c r="A191" s="11">
         <v>45870</v>
       </c>
       <c r="B191" t="s">
@@ -7979,13 +8148,13 @@
       <c r="J191" t="s">
         <v>14</v>
       </c>
-      <c r="K191" s="11">
+      <c r="K191" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A192" s="10">
+      <c r="A192" s="11">
         <v>45870</v>
       </c>
       <c r="B192" t="s">
@@ -8015,13 +8184,13 @@
       <c r="J192" t="s">
         <v>14</v>
       </c>
-      <c r="K192" s="11">
+      <c r="K192" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A193" s="10">
+      <c r="A193" s="11">
         <v>45870</v>
       </c>
       <c r="B193" t="s">
@@ -8051,13 +8220,13 @@
       <c r="J193" t="s">
         <v>14</v>
       </c>
-      <c r="K193" s="11">
+      <c r="K193" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A194" s="10">
+      <c r="A194" s="11">
         <v>45901</v>
       </c>
       <c r="B194" t="s">
@@ -8087,13 +8256,13 @@
       <c r="J194" t="s">
         <v>14</v>
       </c>
-      <c r="K194" s="11">
+      <c r="K194" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A195" s="10">
+      <c r="A195" s="11">
         <v>45901</v>
       </c>
       <c r="B195" t="s">
@@ -8123,13 +8292,13 @@
       <c r="J195" t="s">
         <v>14</v>
       </c>
-      <c r="K195" s="11">
+      <c r="K195" s="12">
         <f t="shared" ref="K195:K258" si="3">IFERROR(H195/E195,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A196" s="10">
+      <c r="A196" s="11">
         <v>45901</v>
       </c>
       <c r="B196" t="s">
@@ -8159,13 +8328,13 @@
       <c r="J196" t="s">
         <v>59</v>
       </c>
-      <c r="K196" s="11">
+      <c r="K196" s="12">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A197" s="10">
+      <c r="A197" s="11">
         <v>45901</v>
       </c>
       <c r="B197" t="s">
@@ -8195,13 +8364,13 @@
       <c r="J197" t="s">
         <v>14</v>
       </c>
-      <c r="K197" s="11">
+      <c r="K197" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A198" s="10">
+      <c r="A198" s="11">
         <v>45901</v>
       </c>
       <c r="B198" t="s">
@@ -8231,13 +8400,13 @@
       <c r="J198" t="s">
         <v>14</v>
       </c>
-      <c r="K198" s="11">
+      <c r="K198" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A199" s="10">
+      <c r="A199" s="11">
         <v>45901</v>
       </c>
       <c r="B199" t="s">
@@ -8267,13 +8436,13 @@
       <c r="J199" t="s">
         <v>14</v>
       </c>
-      <c r="K199" s="11">
+      <c r="K199" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A200" s="10">
+      <c r="A200" s="11">
         <v>45901</v>
       </c>
       <c r="B200" t="s">
@@ -8303,13 +8472,13 @@
       <c r="J200" t="s">
         <v>14</v>
       </c>
-      <c r="K200" s="11">
+      <c r="K200" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A201" s="10">
+      <c r="A201" s="11">
         <v>45901</v>
       </c>
       <c r="B201" t="s">
@@ -8339,13 +8508,13 @@
       <c r="J201" t="s">
         <v>14</v>
       </c>
-      <c r="K201" s="11">
+      <c r="K201" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A202" s="10">
+      <c r="A202" s="11">
         <v>45901</v>
       </c>
       <c r="B202" t="s">
@@ -8375,13 +8544,13 @@
       <c r="J202" t="s">
         <v>14</v>
       </c>
-      <c r="K202" s="11">
+      <c r="K202" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A203" s="10">
+      <c r="A203" s="11">
         <v>45901</v>
       </c>
       <c r="B203" t="s">
@@ -8411,13 +8580,13 @@
       <c r="J203" t="s">
         <v>18</v>
       </c>
-      <c r="K203" s="11">
+      <c r="K203" s="12">
         <f t="shared" si="3"/>
         <v>8.9820359281437126E-2</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A204" s="10">
+      <c r="A204" s="11">
         <v>45901</v>
       </c>
       <c r="B204" t="s">
@@ -8447,13 +8616,13 @@
       <c r="J204" t="s">
         <v>14</v>
       </c>
-      <c r="K204" s="11">
+      <c r="K204" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A205" s="10">
+      <c r="A205" s="11">
         <v>45901</v>
       </c>
       <c r="B205" t="s">
@@ -8483,13 +8652,13 @@
       <c r="J205" t="s">
         <v>18</v>
       </c>
-      <c r="K205" s="11">
+      <c r="K205" s="12">
         <f t="shared" si="3"/>
         <v>8.8607594936708861E-2</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A206" s="10">
+      <c r="A206" s="11">
         <v>45901</v>
       </c>
       <c r="B206" t="s">
@@ -8519,13 +8688,13 @@
       <c r="J206" t="s">
         <v>14</v>
       </c>
-      <c r="K206" s="11">
+      <c r="K206" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A207" s="10">
+      <c r="A207" s="11">
         <v>45901</v>
       </c>
       <c r="B207" t="s">
@@ -8555,13 +8724,13 @@
       <c r="J207" t="s">
         <v>14</v>
       </c>
-      <c r="K207" s="11">
+      <c r="K207" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A208" s="10">
+      <c r="A208" s="11">
         <v>45901</v>
       </c>
       <c r="B208" t="s">
@@ -8591,13 +8760,13 @@
       <c r="J208" t="s">
         <v>14</v>
       </c>
-      <c r="K208" s="11">
+      <c r="K208" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A209" s="10">
+      <c r="A209" s="11">
         <v>45901</v>
       </c>
       <c r="B209" t="s">
@@ -8627,13 +8796,13 @@
       <c r="J209" t="s">
         <v>18</v>
       </c>
-      <c r="K209" s="11">
+      <c r="K209" s="12">
         <f t="shared" si="3"/>
         <v>4.4303797468354431E-2</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A210" s="10">
+      <c r="A210" s="11">
         <v>45901</v>
       </c>
       <c r="B210" t="s">
@@ -8663,13 +8832,13 @@
       <c r="J210" t="s">
         <v>14</v>
       </c>
-      <c r="K210" s="11">
+      <c r="K210" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A211" s="10">
+      <c r="A211" s="11">
         <v>45901</v>
       </c>
       <c r="B211" t="s">
@@ -8699,13 +8868,13 @@
       <c r="J211" t="s">
         <v>14</v>
       </c>
-      <c r="K211" s="11">
+      <c r="K211" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A212" s="10">
+      <c r="A212" s="11">
         <v>45901</v>
       </c>
       <c r="B212" t="s">
@@ -8735,13 +8904,13 @@
       <c r="J212" t="s">
         <v>14</v>
       </c>
-      <c r="K212" s="11">
+      <c r="K212" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A213" s="10">
+      <c r="A213" s="11">
         <v>45901</v>
       </c>
       <c r="B213" t="s">
@@ -8771,13 +8940,13 @@
       <c r="J213" t="s">
         <v>14</v>
       </c>
-      <c r="K213" s="11">
+      <c r="K213" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A214" s="10">
+      <c r="A214" s="11">
         <v>45901</v>
       </c>
       <c r="B214" t="s">
@@ -8807,13 +8976,13 @@
       <c r="J214" t="s">
         <v>14</v>
       </c>
-      <c r="K214" s="11">
+      <c r="K214" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A215" s="10">
+      <c r="A215" s="11">
         <v>45901</v>
       </c>
       <c r="B215" t="s">
@@ -8843,13 +9012,13 @@
       <c r="J215" t="s">
         <v>14</v>
       </c>
-      <c r="K215" s="11">
+      <c r="K215" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A216" s="10">
+      <c r="A216" s="11">
         <v>45901</v>
       </c>
       <c r="B216" t="s">
@@ -8879,13 +9048,13 @@
       <c r="J216" t="s">
         <v>14</v>
       </c>
-      <c r="K216" s="11">
+      <c r="K216" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A217" s="10">
+      <c r="A217" s="11">
         <v>45901</v>
       </c>
       <c r="B217" t="s">
@@ -8915,13 +9084,13 @@
       <c r="J217" t="s">
         <v>18</v>
       </c>
-      <c r="K217" s="11">
+      <c r="K217" s="12">
         <f t="shared" si="3"/>
         <v>4.4303797468354431E-2</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A218" s="10">
+      <c r="A218" s="11">
         <v>45931</v>
       </c>
       <c r="B218" t="s">
@@ -8951,13 +9120,13 @@
       <c r="J218" t="s">
         <v>18</v>
       </c>
-      <c r="K218" s="11">
+      <c r="K218" s="12">
         <f t="shared" si="3"/>
         <v>0.13475177304964539</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A219" s="10">
+      <c r="A219" s="11">
         <v>45931</v>
       </c>
       <c r="B219" t="s">
@@ -8987,13 +9156,13 @@
       <c r="J219" t="s">
         <v>14</v>
       </c>
-      <c r="K219" s="11">
+      <c r="K219" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A220" s="10">
+      <c r="A220" s="11">
         <v>45931</v>
       </c>
       <c r="B220" t="s">
@@ -9023,13 +9192,13 @@
       <c r="J220" t="s">
         <v>14</v>
       </c>
-      <c r="K220" s="11">
+      <c r="K220" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A221" s="10">
+      <c r="A221" s="11">
         <v>45931</v>
       </c>
       <c r="B221" t="s">
@@ -9059,13 +9228,13 @@
       <c r="J221" t="s">
         <v>14</v>
       </c>
-      <c r="K221" s="11">
+      <c r="K221" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A222" s="10">
+      <c r="A222" s="11">
         <v>45931</v>
       </c>
       <c r="B222" t="s">
@@ -9095,13 +9264,13 @@
       <c r="J222" t="s">
         <v>14</v>
       </c>
-      <c r="K222" s="11">
+      <c r="K222" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A223" s="10">
+      <c r="A223" s="11">
         <v>45931</v>
       </c>
       <c r="B223" t="s">
@@ -9131,13 +9300,13 @@
       <c r="J223" t="s">
         <v>59</v>
       </c>
-      <c r="K223" s="11">
+      <c r="K223" s="12">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A224" s="10">
+      <c r="A224" s="11">
         <v>45931</v>
       </c>
       <c r="B224" t="s">
@@ -9167,13 +9336,13 @@
       <c r="J224" t="s">
         <v>14</v>
       </c>
-      <c r="K224" s="11">
+      <c r="K224" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A225" s="10">
+      <c r="A225" s="11">
         <v>45931</v>
       </c>
       <c r="B225" t="s">
@@ -9203,13 +9372,13 @@
       <c r="J225" t="s">
         <v>14</v>
       </c>
-      <c r="K225" s="11">
+      <c r="K225" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A226" s="10">
+      <c r="A226" s="11">
         <v>45931</v>
       </c>
       <c r="B226" t="s">
@@ -9239,13 +9408,13 @@
       <c r="J226" t="s">
         <v>14</v>
       </c>
-      <c r="K226" s="11">
+      <c r="K226" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A227" s="10">
+      <c r="A227" s="11">
         <v>45931</v>
       </c>
       <c r="B227" t="s">
@@ -9275,13 +9444,13 @@
       <c r="J227" t="s">
         <v>14</v>
       </c>
-      <c r="K227" s="11">
+      <c r="K227" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A228" s="10">
+      <c r="A228" s="11">
         <v>45931</v>
       </c>
       <c r="B228" t="s">
@@ -9311,13 +9480,13 @@
       <c r="J228" t="s">
         <v>14</v>
       </c>
-      <c r="K228" s="11">
+      <c r="K228" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A229" s="10">
+      <c r="A229" s="11">
         <v>45931</v>
       </c>
       <c r="B229" t="s">
@@ -9347,13 +9516,13 @@
       <c r="J229" t="s">
         <v>14</v>
       </c>
-      <c r="K229" s="11">
+      <c r="K229" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A230" s="10">
+      <c r="A230" s="11">
         <v>45931</v>
       </c>
       <c r="B230" t="s">
@@ -9383,13 +9552,13 @@
       <c r="J230" t="s">
         <v>59</v>
       </c>
-      <c r="K230" s="11">
+      <c r="K230" s="12">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A231" s="10">
+      <c r="A231" s="11">
         <v>45931</v>
       </c>
       <c r="B231" t="s">
@@ -9419,13 +9588,13 @@
       <c r="J231" t="s">
         <v>14</v>
       </c>
-      <c r="K231" s="11">
+      <c r="K231" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A232" s="10">
+      <c r="A232" s="11">
         <v>45931</v>
       </c>
       <c r="B232" t="s">
@@ -9455,13 +9624,13 @@
       <c r="J232" t="s">
         <v>14</v>
       </c>
-      <c r="K232" s="11">
+      <c r="K232" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A233" s="10">
+      <c r="A233" s="11">
         <v>45931</v>
       </c>
       <c r="B233" t="s">
@@ -9491,13 +9660,13 @@
       <c r="J233" t="s">
         <v>14</v>
       </c>
-      <c r="K233" s="11">
+      <c r="K233" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A234" s="10">
+      <c r="A234" s="11">
         <v>45931</v>
       </c>
       <c r="B234" t="s">
@@ -9527,13 +9696,13 @@
       <c r="J234" t="s">
         <v>14</v>
       </c>
-      <c r="K234" s="11">
+      <c r="K234" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A235" s="10">
+      <c r="A235" s="11">
         <v>45931</v>
       </c>
       <c r="B235" t="s">
@@ -9563,13 +9732,13 @@
       <c r="J235" t="s">
         <v>18</v>
       </c>
-      <c r="K235" s="11">
+      <c r="K235" s="12">
         <f t="shared" si="3"/>
         <v>9.4339622641509441E-2</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A236" s="10">
+      <c r="A236" s="11">
         <v>45931</v>
       </c>
       <c r="B236" t="s">
@@ -9599,13 +9768,13 @@
       <c r="J236" t="s">
         <v>38</v>
       </c>
-      <c r="K236" s="11">
+      <c r="K236" s="12">
         <f t="shared" si="3"/>
         <v>0.31914893617021278</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A237" s="10">
+      <c r="A237" s="11">
         <v>45931</v>
       </c>
       <c r="B237" t="s">
@@ -9635,13 +9804,13 @@
       <c r="J237" t="s">
         <v>14</v>
       </c>
-      <c r="K237" s="11">
+      <c r="K237" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A238" s="10">
+      <c r="A238" s="11">
         <v>45931</v>
       </c>
       <c r="B238" t="s">
@@ -9671,13 +9840,13 @@
       <c r="J238" t="s">
         <v>14</v>
       </c>
-      <c r="K238" s="11">
+      <c r="K238" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A239" s="10">
+      <c r="A239" s="11">
         <v>45931</v>
       </c>
       <c r="B239" t="s">
@@ -9707,13 +9876,13 @@
       <c r="J239" t="s">
         <v>14</v>
       </c>
-      <c r="K239" s="11">
+      <c r="K239" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A240" s="10">
+      <c r="A240" s="11">
         <v>45931</v>
       </c>
       <c r="B240" t="s">
@@ -9743,13 +9912,13 @@
       <c r="J240" t="s">
         <v>14</v>
       </c>
-      <c r="K240" s="11">
+      <c r="K240" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A241" s="10">
+      <c r="A241" s="11">
         <v>45931</v>
       </c>
       <c r="B241" t="s">
@@ -9779,13 +9948,13 @@
       <c r="J241" t="s">
         <v>14</v>
       </c>
-      <c r="K241" s="11">
+      <c r="K241" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A242" s="10">
+      <c r="A242" s="11">
         <v>45962</v>
       </c>
       <c r="B242" t="s">
@@ -9815,13 +9984,13 @@
       <c r="J242" t="s">
         <v>14</v>
       </c>
-      <c r="K242" s="11">
+      <c r="K242" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A243" s="10">
+      <c r="A243" s="11">
         <v>45962</v>
       </c>
       <c r="B243" t="s">
@@ -9851,13 +10020,13 @@
       <c r="J243" t="s">
         <v>18</v>
       </c>
-      <c r="K243" s="11">
+      <c r="K243" s="12">
         <f t="shared" si="3"/>
         <v>9.2715231788079472E-2</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A244" s="10">
+      <c r="A244" s="11">
         <v>45962</v>
       </c>
       <c r="B244" t="s">
@@ -9887,13 +10056,13 @@
       <c r="J244" t="s">
         <v>14</v>
       </c>
-      <c r="K244" s="11">
+      <c r="K244" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A245" s="10">
+      <c r="A245" s="11">
         <v>45962</v>
       </c>
       <c r="B245" t="s">
@@ -9923,13 +10092,13 @@
       <c r="J245" t="s">
         <v>14</v>
       </c>
-      <c r="K245" s="11">
+      <c r="K245" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A246" s="10">
+      <c r="A246" s="11">
         <v>45962</v>
       </c>
       <c r="B246" t="s">
@@ -9959,13 +10128,13 @@
       <c r="J246" t="s">
         <v>14</v>
       </c>
-      <c r="K246" s="11">
+      <c r="K246" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A247" s="10">
+      <c r="A247" s="11">
         <v>45962</v>
       </c>
       <c r="B247" t="s">
@@ -9995,13 +10164,13 @@
       <c r="J247" t="s">
         <v>38</v>
       </c>
-      <c r="K247" s="11">
+      <c r="K247" s="12">
         <f t="shared" si="3"/>
         <v>0.47682119205298013</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A248" s="10">
+      <c r="A248" s="11">
         <v>45962</v>
       </c>
       <c r="B248" t="s">
@@ -10031,13 +10200,13 @@
       <c r="J248" t="s">
         <v>14</v>
       </c>
-      <c r="K248" s="11">
+      <c r="K248" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A249" s="10">
+      <c r="A249" s="11">
         <v>45962</v>
       </c>
       <c r="B249" t="s">
@@ -10067,13 +10236,13 @@
       <c r="J249" t="s">
         <v>18</v>
       </c>
-      <c r="K249" s="11">
+      <c r="K249" s="12">
         <f t="shared" si="3"/>
         <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A250" s="10">
+      <c r="A250" s="11">
         <v>45962</v>
       </c>
       <c r="B250" t="s">
@@ -10103,13 +10272,13 @@
       <c r="J250" t="s">
         <v>14</v>
       </c>
-      <c r="K250" s="11">
+      <c r="K250" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A251" s="10">
+      <c r="A251" s="11">
         <v>45962</v>
       </c>
       <c r="B251" t="s">
@@ -10139,13 +10308,13 @@
       <c r="J251" t="s">
         <v>14</v>
       </c>
-      <c r="K251" s="11">
+      <c r="K251" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A252" s="10">
+      <c r="A252" s="11">
         <v>45962</v>
       </c>
       <c r="B252" t="s">
@@ -10175,13 +10344,13 @@
       <c r="J252" t="s">
         <v>14</v>
       </c>
-      <c r="K252" s="11">
+      <c r="K252" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A253" s="10">
+      <c r="A253" s="11">
         <v>45962</v>
       </c>
       <c r="B253" t="s">
@@ -10211,13 +10380,13 @@
       <c r="J253" t="s">
         <v>14</v>
       </c>
-      <c r="K253" s="11">
+      <c r="K253" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A254" s="10">
+      <c r="A254" s="11">
         <v>45962</v>
       </c>
       <c r="B254" t="s">
@@ -10247,13 +10416,13 @@
       <c r="J254" t="s">
         <v>14</v>
       </c>
-      <c r="K254" s="11">
+      <c r="K254" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A255" s="10">
+      <c r="A255" s="11">
         <v>45962</v>
       </c>
       <c r="B255" t="s">
@@ -10283,13 +10452,13 @@
       <c r="J255" t="s">
         <v>14</v>
       </c>
-      <c r="K255" s="11">
+      <c r="K255" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A256" s="10">
+      <c r="A256" s="11">
         <v>45962</v>
       </c>
       <c r="B256" t="s">
@@ -10319,13 +10488,13 @@
       <c r="J256" t="s">
         <v>14</v>
       </c>
-      <c r="K256" s="11">
+      <c r="K256" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A257" s="10">
+      <c r="A257" s="11">
         <v>45962</v>
       </c>
       <c r="B257" t="s">
@@ -10355,13 +10524,13 @@
       <c r="J257" t="s">
         <v>14</v>
       </c>
-      <c r="K257" s="11">
+      <c r="K257" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A258" s="10">
+      <c r="A258" s="11">
         <v>45962</v>
       </c>
       <c r="B258" t="s">
@@ -10391,13 +10560,13 @@
       <c r="J258" t="s">
         <v>18</v>
       </c>
-      <c r="K258" s="11">
+      <c r="K258" s="12">
         <f t="shared" si="3"/>
         <v>4.4776119402985072E-2</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A259" s="10">
+      <c r="A259" s="11">
         <v>45962</v>
       </c>
       <c r="B259" t="s">
@@ -10427,13 +10596,13 @@
       <c r="J259" t="s">
         <v>14</v>
       </c>
-      <c r="K259" s="11">
+      <c r="K259" s="12">
         <f t="shared" ref="K259:K289" si="4">IFERROR(H259/E259,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A260" s="10">
+      <c r="A260" s="11">
         <v>45962</v>
       </c>
       <c r="B260" t="s">
@@ -10463,13 +10632,13 @@
       <c r="J260" t="s">
         <v>14</v>
       </c>
-      <c r="K260" s="11">
+      <c r="K260" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A261" s="10">
+      <c r="A261" s="11">
         <v>45962</v>
       </c>
       <c r="B261" t="s">
@@ -10499,13 +10668,13 @@
       <c r="J261" t="s">
         <v>18</v>
       </c>
-      <c r="K261" s="11">
+      <c r="K261" s="12">
         <f t="shared" si="4"/>
         <v>0.05</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A262" s="10">
+      <c r="A262" s="11">
         <v>45962</v>
       </c>
       <c r="B262" t="s">
@@ -10535,13 +10704,13 @@
       <c r="J262" t="s">
         <v>14</v>
       </c>
-      <c r="K262" s="11">
+      <c r="K262" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A263" s="10">
+      <c r="A263" s="11">
         <v>45962</v>
       </c>
       <c r="B263" t="s">
@@ -10571,13 +10740,13 @@
       <c r="J263" t="s">
         <v>14</v>
       </c>
-      <c r="K263" s="11">
+      <c r="K263" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A264" s="10">
+      <c r="A264" s="11">
         <v>45962</v>
       </c>
       <c r="B264" t="s">
@@ -10607,13 +10776,13 @@
       <c r="J264" t="s">
         <v>14</v>
       </c>
-      <c r="K264" s="11">
+      <c r="K264" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A265" s="10">
+      <c r="A265" s="11">
         <v>45962</v>
       </c>
       <c r="B265" t="s">
@@ -10643,13 +10812,13 @@
       <c r="J265" t="s">
         <v>14</v>
       </c>
-      <c r="K265" s="11">
+      <c r="K265" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A266" s="10">
+      <c r="A266" s="11">
         <v>45992</v>
       </c>
       <c r="B266" t="s">
@@ -10679,13 +10848,13 @@
       <c r="J266" t="s">
         <v>14</v>
       </c>
-      <c r="K266" s="11">
+      <c r="K266" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A267" s="10">
+      <c r="A267" s="11">
         <v>45992</v>
       </c>
       <c r="B267" t="s">
@@ -10715,13 +10884,13 @@
       <c r="J267" t="s">
         <v>14</v>
       </c>
-      <c r="K267" s="11">
+      <c r="K267" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A268" s="10">
+      <c r="A268" s="11">
         <v>45992</v>
       </c>
       <c r="B268" t="s">
@@ -10751,13 +10920,13 @@
       <c r="J268" t="s">
         <v>18</v>
       </c>
-      <c r="K268" s="11">
+      <c r="K268" s="12">
         <f t="shared" si="4"/>
         <v>9.9009900990099015E-2</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A269" s="10">
+      <c r="A269" s="11">
         <v>45992</v>
       </c>
       <c r="B269" t="s">
@@ -10787,13 +10956,13 @@
       <c r="J269" t="s">
         <v>14</v>
       </c>
-      <c r="K269" s="11">
+      <c r="K269" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A270" s="10">
+      <c r="A270" s="11">
         <v>45992</v>
       </c>
       <c r="B270" t="s">
@@ -10823,13 +10992,13 @@
       <c r="J270" t="s">
         <v>14</v>
       </c>
-      <c r="K270" s="11">
+      <c r="K270" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A271" s="10">
+      <c r="A271" s="11">
         <v>45992</v>
       </c>
       <c r="B271" t="s">
@@ -10859,13 +11028,13 @@
       <c r="J271" t="s">
         <v>14</v>
       </c>
-      <c r="K271" s="11">
+      <c r="K271" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A272" s="10">
+      <c r="A272" s="11">
         <v>45992</v>
       </c>
       <c r="B272" t="s">
@@ -10895,13 +11064,13 @@
       <c r="J272" t="s">
         <v>14</v>
       </c>
-      <c r="K272" s="11">
+      <c r="K272" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A273" s="10">
+      <c r="A273" s="11">
         <v>45992</v>
       </c>
       <c r="B273" t="s">
@@ -10931,13 +11100,13 @@
       <c r="J273" t="s">
         <v>38</v>
       </c>
-      <c r="K273" s="11">
+      <c r="K273" s="12">
         <f t="shared" si="4"/>
         <v>0.61904761904761907</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A274" s="10">
+      <c r="A274" s="11">
         <v>45992</v>
       </c>
       <c r="B274" t="s">
@@ -10967,13 +11136,13 @@
       <c r="J274" t="s">
         <v>14</v>
       </c>
-      <c r="K274" s="11">
+      <c r="K274" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A275" s="10">
+      <c r="A275" s="11">
         <v>45992</v>
       </c>
       <c r="B275" t="s">
@@ -11003,13 +11172,13 @@
       <c r="J275" t="s">
         <v>14</v>
       </c>
-      <c r="K275" s="11">
+      <c r="K275" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A276" s="10">
+      <c r="A276" s="11">
         <v>45992</v>
       </c>
       <c r="B276" t="s">
@@ -11039,13 +11208,13 @@
       <c r="J276" t="s">
         <v>14</v>
       </c>
-      <c r="K276" s="11">
+      <c r="K276" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A277" s="10">
+      <c r="A277" s="11">
         <v>45992</v>
       </c>
       <c r="B277" t="s">
@@ -11075,13 +11244,13 @@
       <c r="J277" t="s">
         <v>14</v>
       </c>
-      <c r="K277" s="11">
+      <c r="K277" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A278" s="10">
+      <c r="A278" s="11">
         <v>45992</v>
       </c>
       <c r="B278" t="s">
@@ -11111,13 +11280,13 @@
       <c r="J278" t="s">
         <v>14</v>
       </c>
-      <c r="K278" s="11">
+      <c r="K278" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A279" s="10">
+      <c r="A279" s="11">
         <v>45992</v>
       </c>
       <c r="B279" t="s">
@@ -11147,13 +11316,13 @@
       <c r="J279" t="s">
         <v>14</v>
       </c>
-      <c r="K279" s="11">
+      <c r="K279" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A280" s="10">
+      <c r="A280" s="11">
         <v>45992</v>
       </c>
       <c r="B280" t="s">
@@ -11183,13 +11352,13 @@
       <c r="J280" t="s">
         <v>59</v>
       </c>
-      <c r="K280" s="11">
+      <c r="K280" s="12">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A281" s="10">
+      <c r="A281" s="11">
         <v>45992</v>
       </c>
       <c r="B281" t="s">
@@ -11219,13 +11388,13 @@
       <c r="J281" t="s">
         <v>14</v>
       </c>
-      <c r="K281" s="11">
+      <c r="K281" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A282" s="10">
+      <c r="A282" s="11">
         <v>45992</v>
       </c>
       <c r="B282" t="s">
@@ -11255,13 +11424,13 @@
       <c r="J282" t="s">
         <v>14</v>
       </c>
-      <c r="K282" s="11">
+      <c r="K282" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A283" s="10">
+      <c r="A283" s="11">
         <v>45992</v>
       </c>
       <c r="B283" t="s">
@@ -11291,13 +11460,13 @@
       <c r="J283" t="s">
         <v>18</v>
       </c>
-      <c r="K283" s="11">
+      <c r="K283" s="12">
         <f t="shared" si="4"/>
         <v>9.9009900990099015E-2</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A284" s="10">
+      <c r="A284" s="11">
         <v>45992</v>
       </c>
       <c r="B284" t="s">
@@ -11327,13 +11496,13 @@
       <c r="J284" t="s">
         <v>14</v>
       </c>
-      <c r="K284" s="11">
+      <c r="K284" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A285" s="10">
+      <c r="A285" s="11">
         <v>45992</v>
       </c>
       <c r="B285" t="s">
@@ -11363,13 +11532,13 @@
       <c r="J285" t="s">
         <v>14</v>
       </c>
-      <c r="K285" s="11">
+      <c r="K285" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A286" s="10">
+      <c r="A286" s="11">
         <v>45992</v>
       </c>
       <c r="B286" t="s">
@@ -11399,13 +11568,13 @@
       <c r="J286" t="s">
         <v>18</v>
       </c>
-      <c r="K286" s="11">
+      <c r="K286" s="12">
         <f t="shared" si="4"/>
         <v>9.2715231788079472E-2</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A287" s="10">
+      <c r="A287" s="11">
         <v>45992</v>
       </c>
       <c r="B287" t="s">
@@ -11435,13 +11604,13 @@
       <c r="J287" t="s">
         <v>14</v>
       </c>
-      <c r="K287" s="11">
+      <c r="K287" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A288" s="10">
+      <c r="A288" s="11">
         <v>45992</v>
       </c>
       <c r="B288" t="s">
@@ -11471,13 +11640,13 @@
       <c r="J288" t="s">
         <v>59</v>
       </c>
-      <c r="K288" s="11">
+      <c r="K288" s="12">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A289" s="10">
+      <c r="A289" s="11">
         <v>45992</v>
       </c>
       <c r="B289" t="s">
@@ -11507,7 +11676,7 @@
       <c r="J289" t="s">
         <v>14</v>
       </c>
-      <c r="K289" s="11">
+      <c r="K289" s="12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -11518,4 +11687,1116 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{050C72D5-0058-AD4E-A65E-E62174395E10}">
+  <dimension ref="A1:M50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="13" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="22" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A6)</f>
+        <v>894</v>
+      </c>
+      <c r="C6" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A6)</f>
+        <v>9786</v>
+      </c>
+      <c r="D6" s="12">
+        <f>IFERROR(B6/C6,0)</f>
+        <v>9.1354996934396082E-2</v>
+      </c>
+      <c r="E6" s="1">
+        <f>SUMIFS(Registratie[Overuren],Registratie[Afdeling],$A6)</f>
+        <v>125</v>
+      </c>
+      <c r="F6" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A6,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>573</v>
+      </c>
+      <c r="G6" s="1" cm="1">
+        <f t="array" ref="G6">COUNTA(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Registratie[Medewerker],Registratie[Afdeling]=$A6)))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A7)</f>
+        <v>501</v>
+      </c>
+      <c r="C7" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A7)</f>
+        <v>7953</v>
+      </c>
+      <c r="D7" s="12">
+        <f t="shared" ref="D7:D11" si="0">IFERROR(B7/C7,0)</f>
+        <v>6.2995096190116937E-2</v>
+      </c>
+      <c r="E7" s="1">
+        <f>SUMIFS(Registratie[Overuren],Registratie[Afdeling],$A7)</f>
+        <v>139</v>
+      </c>
+      <c r="F7" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A7,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>224</v>
+      </c>
+      <c r="G7" s="1" cm="1">
+        <f t="array" ref="G7">COUNTA(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Registratie[Medewerker],Registratie[Afdeling]=$A7)))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A8)</f>
+        <v>296</v>
+      </c>
+      <c r="C8" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A8)</f>
+        <v>6322</v>
+      </c>
+      <c r="D8" s="12">
+        <f t="shared" si="0"/>
+        <v>4.682062638405568E-2</v>
+      </c>
+      <c r="E8" s="1">
+        <f>SUMIFS(Registratie[Overuren],Registratie[Afdeling],$A8)</f>
+        <v>92</v>
+      </c>
+      <c r="F8" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A8,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>96</v>
+      </c>
+      <c r="G8" s="1" cm="1">
+        <f t="array" ref="G8">COUNTA(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Registratie[Medewerker],Registratie[Afdeling]=$A8)))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A9)</f>
+        <v>303</v>
+      </c>
+      <c r="C9" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A9)</f>
+        <v>6529</v>
+      </c>
+      <c r="D9" s="12">
+        <f t="shared" si="0"/>
+        <v>4.6408332056976566E-2</v>
+      </c>
+      <c r="E9" s="1">
+        <f>SUMIFS(Registratie[Overuren],Registratie[Afdeling],$A9)</f>
+        <v>75</v>
+      </c>
+      <c r="F9" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A9,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>160</v>
+      </c>
+      <c r="G9" s="1" cm="1">
+        <f t="array" ref="G9">COUNTA(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Registratie[Medewerker],Registratie[Afdeling]=$A9)))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A10)</f>
+        <v>180</v>
+      </c>
+      <c r="C10" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A10)</f>
+        <v>9069</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" si="0"/>
+        <v>1.9847833278200461E-2</v>
+      </c>
+      <c r="E10" s="1">
+        <f>SUMIFS(Registratie[Overuren],Registratie[Afdeling],$A10)</f>
+        <v>118</v>
+      </c>
+      <c r="F10" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A10,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>151</v>
+      </c>
+      <c r="G10" s="1" cm="1">
+        <f t="array" ref="G10">COUNTA(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Registratie[Medewerker],Registratie[Afdeling]=$A10)))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" s="15">
+        <f>SUM(B6:B10)</f>
+        <v>2174</v>
+      </c>
+      <c r="C11" s="15">
+        <f>SUM(C6:C10)</f>
+        <v>39659</v>
+      </c>
+      <c r="D11" s="14">
+        <f>IFERROR(B11/C11,0)</f>
+        <v>5.4817317632819787E-2</v>
+      </c>
+      <c r="E11" s="15">
+        <f>SUM(E6:E10)</f>
+        <v>549</v>
+      </c>
+      <c r="F11" s="15">
+        <f>SUM(F6:F10)</f>
+        <v>1204</v>
+      </c>
+      <c r="G11" s="15">
+        <f>SUM(G6:G10)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="A14" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="11">
+        <v>45658</v>
+      </c>
+      <c r="B15" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A15)</f>
+        <v>139</v>
+      </c>
+      <c r="C15" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Maand],$A15)</f>
+        <v>3421</v>
+      </c>
+      <c r="D15" s="12">
+        <f>IFERROR(B15/C15,0)</f>
+        <v>4.0631394329143526E-2</v>
+      </c>
+      <c r="E15" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A15,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="12">
+        <f>IFERROR(E15/B15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="12">
+        <f>IFERROR((B15-E15)/C15,0)</f>
+        <v>4.0631394329143526E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="11">
+        <v>45689</v>
+      </c>
+      <c r="B16" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A16)</f>
+        <v>252</v>
+      </c>
+      <c r="C16" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Maand],$A16)</f>
+        <v>3112</v>
+      </c>
+      <c r="D16" s="12">
+        <f t="shared" ref="D16:D26" si="1">IFERROR(B16/C16,0)</f>
+        <v>8.0976863753213363E-2</v>
+      </c>
+      <c r="E16" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A16,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>96</v>
+      </c>
+      <c r="F16" s="12">
+        <f t="shared" ref="F16:F27" si="2">IFERROR(E16/B16,0)</f>
+        <v>0.38095238095238093</v>
+      </c>
+      <c r="G16" s="12">
+        <f t="shared" ref="G16:G27" si="3">IFERROR((B16-E16)/C16,0)</f>
+        <v>5.0128534704370183E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="11">
+        <v>45717</v>
+      </c>
+      <c r="B17" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A17)</f>
+        <v>51</v>
+      </c>
+      <c r="C17" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Maand],$A17)</f>
+        <v>3421</v>
+      </c>
+      <c r="D17" s="12">
+        <f t="shared" si="1"/>
+        <v>1.4907921660333235E-2</v>
+      </c>
+      <c r="E17" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A17,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="12">
+        <f t="shared" si="3"/>
+        <v>1.4907921660333235E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="11">
+        <v>45748</v>
+      </c>
+      <c r="B18" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A18)</f>
+        <v>16</v>
+      </c>
+      <c r="C18" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Maand],$A18)</f>
+        <v>3112</v>
+      </c>
+      <c r="D18" s="12">
+        <f t="shared" si="1"/>
+        <v>5.1413881748071976E-3</v>
+      </c>
+      <c r="E18" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A18,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="12">
+        <f t="shared" si="3"/>
+        <v>5.1413881748071976E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="11">
+        <v>45778</v>
+      </c>
+      <c r="B19" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A19)</f>
+        <v>209</v>
+      </c>
+      <c r="C19" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Maand],$A19)</f>
+        <v>3266</v>
+      </c>
+      <c r="D19" s="12">
+        <f t="shared" si="1"/>
+        <v>6.3992651561543171E-2</v>
+      </c>
+      <c r="E19" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A19,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>151</v>
+      </c>
+      <c r="F19" s="12">
+        <f t="shared" si="2"/>
+        <v>0.72248803827751196</v>
+      </c>
+      <c r="G19" s="12">
+        <f t="shared" si="3"/>
+        <v>1.7758726270667484E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="11">
+        <v>45809</v>
+      </c>
+      <c r="B20" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A20)</f>
+        <v>277</v>
+      </c>
+      <c r="C20" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Maand],$A20)</f>
+        <v>3266</v>
+      </c>
+      <c r="D20" s="12">
+        <f t="shared" si="1"/>
+        <v>8.4813227189222296E-2</v>
+      </c>
+      <c r="E20" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A20,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>160</v>
+      </c>
+      <c r="F20" s="12">
+        <f t="shared" si="2"/>
+        <v>0.57761732851985559</v>
+      </c>
+      <c r="G20" s="12">
+        <f t="shared" si="3"/>
+        <v>3.5823637477036131E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="11">
+        <v>45839</v>
+      </c>
+      <c r="B21" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A21)</f>
+        <v>237</v>
+      </c>
+      <c r="C21" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Maand],$A21)</f>
+        <v>3421</v>
+      </c>
+      <c r="D21" s="12">
+        <f t="shared" si="1"/>
+        <v>6.9277988892136808E-2</v>
+      </c>
+      <c r="E21" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A21,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>158</v>
+      </c>
+      <c r="F21" s="12">
+        <f t="shared" si="2"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G21" s="12">
+        <f t="shared" si="3"/>
+        <v>2.30926629640456E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="11">
+        <v>45870</v>
+      </c>
+      <c r="B22" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A22)</f>
+        <v>39</v>
+      </c>
+      <c r="C22" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Maand],$A22)</f>
+        <v>3266</v>
+      </c>
+      <c r="D22" s="12">
+        <f t="shared" si="1"/>
+        <v>1.1941212492345376E-2</v>
+      </c>
+      <c r="E22" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A22,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="12">
+        <f t="shared" si="3"/>
+        <v>1.1941212492345376E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="11">
+        <v>45901</v>
+      </c>
+      <c r="B23" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A23)</f>
+        <v>149</v>
+      </c>
+      <c r="C23" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Maand],$A23)</f>
+        <v>3421</v>
+      </c>
+      <c r="D23" s="12">
+        <f t="shared" si="1"/>
+        <v>4.3554516223326512E-2</v>
+      </c>
+      <c r="E23" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A23,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>106</v>
+      </c>
+      <c r="F23" s="12">
+        <f t="shared" si="2"/>
+        <v>0.71140939597315433</v>
+      </c>
+      <c r="G23" s="12">
+        <f t="shared" si="3"/>
+        <v>1.2569424144986846E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="11">
+        <v>45931</v>
+      </c>
+      <c r="B24" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A24)</f>
+        <v>338</v>
+      </c>
+      <c r="C24" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Maand],$A24)</f>
+        <v>3421</v>
+      </c>
+      <c r="D24" s="12">
+        <f t="shared" si="1"/>
+        <v>9.8801520023384978E-2</v>
+      </c>
+      <c r="E24" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A24,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>264</v>
+      </c>
+      <c r="F24" s="12">
+        <f t="shared" si="2"/>
+        <v>0.78106508875739644</v>
+      </c>
+      <c r="G24" s="12">
+        <f t="shared" si="3"/>
+        <v>2.1631102016954108E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="11">
+        <v>45962</v>
+      </c>
+      <c r="B25" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A25)</f>
+        <v>112</v>
+      </c>
+      <c r="C25" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Maand],$A25)</f>
+        <v>3266</v>
+      </c>
+      <c r="D25" s="12">
+        <f t="shared" si="1"/>
+        <v>3.4292712798530314E-2</v>
+      </c>
+      <c r="E25" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A25,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="12">
+        <f t="shared" si="3"/>
+        <v>3.4292712798530314E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="11">
+        <v>45992</v>
+      </c>
+      <c r="B26" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A26)</f>
+        <v>355</v>
+      </c>
+      <c r="C26" s="1">
+        <f>SUMIFS(Registratie[Contracturen],Registratie[Maand],$A26)</f>
+        <v>3266</v>
+      </c>
+      <c r="D26" s="12">
+        <f t="shared" si="1"/>
+        <v>0.10869565217391304</v>
+      </c>
+      <c r="E26" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Maand],$A26,Registratie[Verzuimsoort],"Langdurig (&gt; 6 wk)")</f>
+        <v>269</v>
+      </c>
+      <c r="F26" s="12">
+        <f t="shared" si="2"/>
+        <v>0.75774647887323943</v>
+      </c>
+      <c r="G26" s="12">
+        <f t="shared" si="3"/>
+        <v>2.6331904470300063E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="15">
+        <f>SUM(B15:B26)</f>
+        <v>2174</v>
+      </c>
+      <c r="C27" s="15">
+        <f>SUM(C15:C26)</f>
+        <v>39659</v>
+      </c>
+      <c r="D27" s="14">
+        <f>IFERROR(B27/C27,0)</f>
+        <v>5.4817317632819787E-2</v>
+      </c>
+      <c r="E27" s="15">
+        <f>SUM(E15:E26)</f>
+        <v>1204</v>
+      </c>
+      <c r="F27" s="14">
+        <f>IFERROR(E27/B27,0)</f>
+        <v>0.55381784728610861</v>
+      </c>
+      <c r="G27" s="14">
+        <f>IFERROR((B27-E27)/C27,0)</f>
+        <v>2.4458508787412694E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Verzuimsoort],$A31)</f>
+        <v>461</v>
+      </c>
+      <c r="C31" s="12">
+        <f>IFERROR(B31/$B$34,0)</f>
+        <v>0.21205151793928242</v>
+      </c>
+      <c r="D31" s="1">
+        <f>COUNTIFS(Registratie[Verzuimsoort],$A31)</f>
+        <v>41</v>
+      </c>
+      <c r="E31" s="1" cm="1">
+        <f t="array" ref="E31">COUNTA(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Registratie[Medewerker],Registratie[Verzuimsoort]=$A31)))</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Verzuimsoort],$A32)</f>
+        <v>509</v>
+      </c>
+      <c r="C32" s="12">
+        <f t="shared" ref="C32:C33" si="4">IFERROR(B32/$B$34,0)</f>
+        <v>0.23413063477460902</v>
+      </c>
+      <c r="D32" s="1">
+        <f>COUNTIFS(Registratie[Verzuimsoort],$A32)</f>
+        <v>9</v>
+      </c>
+      <c r="E32" s="1" cm="1">
+        <f t="array" ref="E32">COUNTA(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Registratie[Medewerker],Registratie[Verzuimsoort]=$A32)))</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="1">
+        <f>SUMIFS(Registratie[Verzuimuren],Registratie[Verzuimsoort],$A33)</f>
+        <v>1204</v>
+      </c>
+      <c r="C33" s="12">
+        <f t="shared" si="4"/>
+        <v>0.55381784728610861</v>
+      </c>
+      <c r="D33" s="1">
+        <f>COUNTIFS(Registratie[Verzuimsoort],$A33)</f>
+        <v>9</v>
+      </c>
+      <c r="E33" s="1" cm="1">
+        <f t="array" ref="E33">COUNTA(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Registratie[Medewerker],Registratie[Verzuimsoort]=$A33)))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="15">
+        <f>SUM(B31:B33)</f>
+        <v>2174</v>
+      </c>
+      <c r="C34" s="14">
+        <f>IFERROR(B34/$B$34,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D34" s="15">
+        <f>SUM(D31:D33)</f>
+        <v>59</v>
+      </c>
+      <c r="E34" s="15" cm="1">
+        <f t="array" ref="E34">COUNTA(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Registratie[Medewerker],Registratie[Verzuimsoort]&lt;&gt;"Geen")))</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="17">
+        <v>45658</v>
+      </c>
+      <c r="C37" s="17">
+        <v>45689</v>
+      </c>
+      <c r="D37" s="17">
+        <v>45717</v>
+      </c>
+      <c r="E37" s="17">
+        <v>45748</v>
+      </c>
+      <c r="F37" s="17">
+        <v>45778</v>
+      </c>
+      <c r="G37" s="17">
+        <v>45809</v>
+      </c>
+      <c r="H37" s="17">
+        <v>45839</v>
+      </c>
+      <c r="I37" s="17">
+        <v>45870</v>
+      </c>
+      <c r="J37" s="17">
+        <v>45901</v>
+      </c>
+      <c r="K37" s="17">
+        <v>45931</v>
+      </c>
+      <c r="L37" s="17">
+        <v>45962</v>
+      </c>
+      <c r="M37" s="17">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A38,Registratie[Maand],B$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A38,Registratie[Maand],B$37),0)</f>
+        <v>5.9241706161137437E-3</v>
+      </c>
+      <c r="C38" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A38,Registratie[Maand],C$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A38,Registratie[Maand],C$37),0)</f>
+        <v>6.640625E-2</v>
+      </c>
+      <c r="D38" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A38,Registratie[Maand],D$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A38,Registratie[Maand],D$37),0)</f>
+        <v>2.2511848341232227E-2</v>
+      </c>
+      <c r="E38" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A38,Registratie[Maand],E$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A38,Registratie[Maand],E$37),0)</f>
+        <v>1.3020833333333334E-2</v>
+      </c>
+      <c r="F38" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A38,Registratie[Maand],F$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A38,Registratie[Maand],F$37),0)</f>
+        <v>0.18734491315136476</v>
+      </c>
+      <c r="G38" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A38,Registratie[Maand],G$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A38,Registratie[Maand],G$37),0)</f>
+        <v>0.11290322580645161</v>
+      </c>
+      <c r="H38" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A38,Registratie[Maand],H$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A38,Registratie[Maand],H$37),0)</f>
+        <v>0.20260663507109006</v>
+      </c>
+      <c r="I38" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A38,Registratie[Maand],I$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A38,Registratie[Maand],I$37),0)</f>
+        <v>2.1091811414392061E-2</v>
+      </c>
+      <c r="J38" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A38,Registratie[Maand],J$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A38,Registratie[Maand],J$37),0)</f>
+        <v>0.12559241706161137</v>
+      </c>
+      <c r="K38" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A38,Registratie[Maand],K$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A38,Registratie[Maand],K$37),0)</f>
+        <v>0.20971563981042654</v>
+      </c>
+      <c r="L38" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A38,Registratie[Maand],L$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A38,Registratie[Maand],L$37),0)</f>
+        <v>0.10669975186104218</v>
+      </c>
+      <c r="M38" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A38,Registratie[Maand],M$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A38,Registratie[Maand],M$37),0)</f>
+        <v>1.2406947890818859E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A39,Registratie[Maand],B$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A39,Registratie[Maand],B$37),0)</f>
+        <v>0.11370262390670553</v>
+      </c>
+      <c r="C39" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A39,Registratie[Maand],C$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A39,Registratie[Maand],C$37),0)</f>
+        <v>6.0897435897435896E-2</v>
+      </c>
+      <c r="D39" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A39,Registratie[Maand],D$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A39,Registratie[Maand],D$37),0)</f>
+        <v>4.6647230320699708E-2</v>
+      </c>
+      <c r="E39" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A39,Registratie[Maand],E$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A39,Registratie[Maand],E$37),0)</f>
+        <v>9.6153846153846159E-3</v>
+      </c>
+      <c r="F39" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A39,Registratie[Maand],F$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A39,Registratie[Maand],F$37),0)</f>
+        <v>1.0687022900763359E-2</v>
+      </c>
+      <c r="G39" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A39,Registratie[Maand],G$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A39,Registratie[Maand],G$37),0)</f>
+        <v>3.3587786259541987E-2</v>
+      </c>
+      <c r="H39" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A39,Registratie[Maand],H$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A39,Registratie[Maand],H$37),0)</f>
+        <v>8.4548104956268216E-2</v>
+      </c>
+      <c r="I39" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A39,Registratie[Maand],I$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A39,Registratie[Maand],I$37),0)</f>
+        <v>3.3587786259541987E-2</v>
+      </c>
+      <c r="J39" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A39,Registratie[Maand],J$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A39,Registratie[Maand],J$37),0)</f>
+        <v>2.0408163265306121E-2</v>
+      </c>
+      <c r="K39" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A39,Registratie[Maand],K$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A39,Registratie[Maand],K$37),0)</f>
+        <v>0.15451895043731778</v>
+      </c>
+      <c r="L39" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A39,Registratie[Maand],L$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A39,Registratie[Maand],L$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A39,Registratie[Maand],M$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A39,Registratie[Maand],M$37),0)</f>
+        <v>0.18015267175572519</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A40,Registratie[Maand],B$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A40,Registratie[Maand],B$37),0)</f>
+        <v>3.6630036630036632E-2</v>
+      </c>
+      <c r="C40" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A40,Registratie[Maand],C$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A40,Registratie[Maand],C$37),0)</f>
+        <v>0.2963709677419355</v>
+      </c>
+      <c r="D40" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A40,Registratie[Maand],D$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A40,Registratie[Maand],D$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A40,Registratie[Maand],E$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A40,Registratie[Maand],E$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A40,Registratie[Maand],F$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A40,Registratie[Maand],F$37),0)</f>
+        <v>9.8076923076923075E-2</v>
+      </c>
+      <c r="G40" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A40,Registratie[Maand],G$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A40,Registratie[Maand],G$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A40,Registratie[Maand],H$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A40,Registratie[Maand],H$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A40,Registratie[Maand],I$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A40,Registratie[Maand],I$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A40,Registratie[Maand],J$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A40,Registratie[Maand],J$37),0)</f>
+        <v>1.282051282051282E-2</v>
+      </c>
+      <c r="K40" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A40,Registratie[Maand],K$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A40,Registratie[Maand],K$37),0)</f>
+        <v>0.10073260073260074</v>
+      </c>
+      <c r="L40" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A40,Registratie[Maand],L$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A40,Registratie[Maand],L$37),0)</f>
+        <v>1.1538461538461539E-2</v>
+      </c>
+      <c r="M40" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A40,Registratie[Maand],M$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A40,Registratie[Maand],M$37),0)</f>
+        <v>1.9230769230769232E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A41,Registratie[Maand],B$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A41,Registratie[Maand],B$37),0)</f>
+        <v>6.3943161634103018E-2</v>
+      </c>
+      <c r="C41" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A41,Registratie[Maand],C$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A41,Registratie[Maand],C$37),0)</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="D41" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A41,Registratie[Maand],D$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A41,Registratie[Maand],D$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A41,Registratie[Maand],E$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A41,Registratie[Maand],E$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A41,Registratie[Maand],F$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A41,Registratie[Maand],F$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A41,Registratie[Maand],G$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A41,Registratie[Maand],G$37),0)</f>
+        <v>0.30483271375464682</v>
+      </c>
+      <c r="H41" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A41,Registratie[Maand],H$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A41,Registratie[Maand],H$37),0)</f>
+        <v>1.4209591474245116E-2</v>
+      </c>
+      <c r="I41" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A41,Registratie[Maand],I$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A41,Registratie[Maand],I$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A41,Registratie[Maand],J$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A41,Registratie[Maand],J$37),0)</f>
+        <v>2.664298401420959E-2</v>
+      </c>
+      <c r="K41" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A41,Registratie[Maand],K$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A41,Registratie[Maand],K$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A41,Registratie[Maand],L$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A41,Registratie[Maand],L$37),0)</f>
+        <v>2.2304832713754646E-2</v>
+      </c>
+      <c r="M41" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A41,Registratie[Maand],M$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A41,Registratie[Maand],M$37),0)</f>
+        <v>9.6654275092936809E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A42,Registratie[Maand],B$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A42,Registratie[Maand],B$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C42" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A42,Registratie[Maand],C$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A42,Registratie[Maand],C$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A42,Registratie[Maand],D$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A42,Registratie[Maand],D$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A42,Registratie[Maand],E$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A42,Registratie[Maand],E$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A42,Registratie[Maand],F$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A42,Registratie[Maand],F$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A42,Registratie[Maand],G$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A42,Registratie[Maand],G$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A42,Registratie[Maand],H$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A42,Registratie[Maand],H$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A42,Registratie[Maand],I$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A42,Registratie[Maand],I$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A42,Registratie[Maand],J$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A42,Registratie[Maand],J$37),0)</f>
+        <v>8.9514066496163679E-3</v>
+      </c>
+      <c r="K42" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A42,Registratie[Maand],K$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A42,Registratie[Maand],K$37),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A42,Registratie[Maand],L$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A42,Registratie[Maand],L$37),0)</f>
+        <v>1.0709504685408299E-2</v>
+      </c>
+      <c r="M42" s="12">
+        <f>IFERROR(SUMIFS(Registratie[Verzuimuren],Registratie[Afdeling],$A42,Registratie[Maand],M$37)/SUMIFS(Registratie[Contracturen],Registratie[Afdeling],$A42,Registratie[Maand],M$37),0)</f>
+        <v>0.22088353413654618</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="340" x14ac:dyDescent="0.2">
+      <c r="A45" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="323" x14ac:dyDescent="0.2">
+      <c r="A46" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="272" x14ac:dyDescent="0.2">
+      <c r="A47" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="204" x14ac:dyDescent="0.2">
+      <c r="A48" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="356" x14ac:dyDescent="0.2">
+      <c r="A49" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="187" x14ac:dyDescent="0.2">
+      <c r="A50" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="a8gDPuW776UuMnO4XmPqo8r+q/LSFUzjbFdbt+EbT7tfaRWAZ7poGJ2jR8EoU+FExrFL2c12elEaEyKbZN+7wg==" saltValue="MaKXVvN1dyZHT625HX9whQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <conditionalFormatting sqref="B38:M42">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF4B183"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>